--- a/mlmodel/labeled_output.xlsx
+++ b/mlmodel/labeled_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
+  <dimension ref="A1:I1015"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
         <v>62.94</v>
       </c>
       <c r="H2" t="n">
-        <v>0.184926735089562</v>
+        <v>0.1711147969426532</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
         <v>17.77</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2259411633636079</v>
+        <v>0.2193922903530517</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
         <v>39.8</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1117749288055307</v>
+        <v>0.1084332112489187</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v>5.11</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1344318495148872</v>
+        <v>0.1285309210704755</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         <v>31.38</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1130479944710526</v>
+        <v>0.1030917230938672</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -653,7 +653,7 @@
         <v>15.23</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1363615188165824</v>
+        <v>0.1443597024312346</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
         <v>25.2</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1479391832944078</v>
+        <v>0.1390080093476623</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -715,7 +715,7 @@
         <v>32.15</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09598304914835953</v>
+        <v>0.09656441889299794</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         <v>14.64</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2221895883261621</v>
+        <v>0.2173872422575727</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>53.62</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2007538313947427</v>
+        <v>0.1901924691662868</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>8.25</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2173988722074461</v>
+        <v>0.2136397910535108</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
         <v>13.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0207713167200787</v>
+        <v>0.001506402172502419</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         <v>16.52</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1442693478924371</v>
+        <v>0.1439431952302964</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>12.25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2229092046538053</v>
+        <v>0.2224637716643467</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>41.78</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2211014494884699</v>
+        <v>0.2158368546859607</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>19.06</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1109379661815296</v>
+        <v>0.1011379039444575</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>3.38</v>
       </c>
       <c r="H18" t="n">
-        <v>0.21138668276249</v>
+        <v>0.2100529905736818</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>8.67</v>
       </c>
       <c r="H19" t="n">
-        <v>0.100917899612909</v>
+        <v>0.08850946025789008</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>5.58</v>
       </c>
       <c r="H20" t="n">
-        <v>0.09563791325441706</v>
+        <v>0.0946194605311429</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>9.48</v>
       </c>
       <c r="H21" t="n">
-        <v>0.227053222776229</v>
+        <v>0.2231194625311709</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>4.9</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1302195079527915</v>
+        <v>0.1183907719099944</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1149,11 +1149,11 @@
         <v>177.84</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.001099756683925701</v>
+        <v>0.009875138548777418</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Suspicious</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
         <v>7.88</v>
       </c>
       <c r="H24" t="n">
-        <v>0.09576132001370363</v>
+        <v>0.09295638581864818</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>7.21</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1199963179178639</v>
+        <v>0.1149852279123375</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>56.56</v>
       </c>
       <c r="H26" t="n">
-        <v>0.07470847927006619</v>
+        <v>0.06611430478652158</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>25.92</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2236588018368252</v>
+        <v>0.2180000823853528</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>19.5</v>
       </c>
       <c r="H28" t="n">
-        <v>0.02167541973445908</v>
+        <v>0.02356887021052456</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>12.42</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1364760274367672</v>
+        <v>0.1340430981005455</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v>1.64</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1771291993304072</v>
+        <v>0.1791432641835774</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>5.63</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1017097104787064</v>
+        <v>0.09535150942303527</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>70.18000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1760947179735708</v>
+        <v>0.1619097501747809</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>12.9</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2123226941608673</v>
+        <v>0.2089349357905709</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>1.35</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2025666992533283</v>
+        <v>0.2049037234130606</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>3.82</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.01446000436326866</v>
+        <v>-0.0117795691401239</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>43.5</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2097832393096093</v>
+        <v>0.2069820947572741</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>29.48</v>
       </c>
       <c r="H37" t="n">
-        <v>0.07024526821256127</v>
+        <v>0.0550721792811758</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>53.77</v>
       </c>
       <c r="H38" t="n">
-        <v>0.01581925369979764</v>
+        <v>0.002427155316202079</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>16.41</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1635166358572933</v>
+        <v>0.1725232506688103</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>38.29</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1892278856748245</v>
+        <v>0.180622305539198</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>15.76</v>
       </c>
       <c r="H41" t="n">
-        <v>0.229130502669852</v>
+        <v>0.2212172499044101</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>4.15</v>
       </c>
       <c r="H42" t="n">
-        <v>0.09240441288274104</v>
+        <v>0.09004384384287878</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1769,7 +1769,7 @@
         <v>17.81</v>
       </c>
       <c r="H43" t="n">
-        <v>0.04033212472551817</v>
+        <v>0.037748810466118</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>44.03</v>
       </c>
       <c r="H44" t="n">
-        <v>0.2221380242641277</v>
+        <v>0.2138643460523225</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>13.18</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1952416497256495</v>
+        <v>0.1911427243267139</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>11.76</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1075605208331968</v>
+        <v>0.1052080011900847</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>67.11</v>
       </c>
       <c r="H47" t="n">
-        <v>0.1712684626177657</v>
+        <v>0.1647082433770005</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0.2255862383523862</v>
+        <v>0.2227979456587234</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>9.640000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>0.213434966551282</v>
+        <v>0.20497148665915</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>6.49</v>
       </c>
       <c r="H50" t="n">
-        <v>0.1337996051107986</v>
+        <v>0.1257117171057216</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>20.51</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2395818396331455</v>
+        <v>0.2304375164999833</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>2.94</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.01035510098919534</v>
+        <v>-0.01317387231412248</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>0.2084548876597203</v>
+        <v>0.1995700848258954</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
         <v>1.86</v>
       </c>
       <c r="H54" t="n">
-        <v>0.1251531362114773</v>
+        <v>0.1240010388985675</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>1.09</v>
       </c>
       <c r="H55" t="n">
-        <v>0.1073879251999783</v>
+        <v>0.1045690266929024</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>1.42</v>
       </c>
       <c r="H56" t="n">
-        <v>0.1179968412904574</v>
+        <v>0.1117786891538884</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>3.39</v>
       </c>
       <c r="H57" t="n">
-        <v>0.09621756048401287</v>
+        <v>0.0860575993324818</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>84.68000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>0.07475325258052501</v>
+        <v>0.07654813650587156</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>77.73999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>0.1549399602419765</v>
+        <v>0.1495839449165944</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>40.04</v>
       </c>
       <c r="H60" t="n">
-        <v>0.2227441868409165</v>
+        <v>0.2164002592293891</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>9.51</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.009301027339607804</v>
+        <v>-0.01006990377910133</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2358,11 +2358,11 @@
         <v>2.99</v>
       </c>
       <c r="H62" t="n">
-        <v>0.005686340706744231</v>
+        <v>-0.01091275986341556</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Suspicious</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
         <v>4.03</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1112408871689103</v>
+        <v>0.1041828846217179</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>20.7</v>
       </c>
       <c r="H64" t="n">
-        <v>0.1458550065160826</v>
+        <v>0.1422492065810964</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>11.39</v>
       </c>
       <c r="H65" t="n">
-        <v>0.2116067051487622</v>
+        <v>0.2044041188490446</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2482,7 +2482,7 @@
         <v>30.89</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2301585783857253</v>
+        <v>0.2248321303043793</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2513,7 +2513,7 @@
         <v>4.53</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1234062528368524</v>
+        <v>0.1179297106858291</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>13.56</v>
       </c>
       <c r="H68" t="n">
-        <v>0.2348287567825814</v>
+        <v>0.2276887602796086</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>13.07</v>
       </c>
       <c r="H69" t="n">
-        <v>0.004736598655159852</v>
+        <v>0.01435700947308571</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>79.33</v>
       </c>
       <c r="H70" t="n">
-        <v>0.1348715961121697</v>
+        <v>0.1255695493146257</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>10.25</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2177534870322186</v>
+        <v>0.2102244387691211</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>32.08</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2207068942130528</v>
+        <v>0.2098534061568882</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>8.75</v>
       </c>
       <c r="H73" t="n">
-        <v>0.07440462544502169</v>
+        <v>0.08660747666323909</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>7.55</v>
       </c>
       <c r="H74" t="n">
-        <v>0.2246550613796371</v>
+        <v>0.2195482256327255</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -2761,7 +2761,7 @@
         <v>6.08</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1266310388356032</v>
+        <v>0.1217214159696491</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
         <v>14.94</v>
       </c>
       <c r="H76" t="n">
-        <v>0.1513585918202385</v>
+        <v>0.149142317400816</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>59.06</v>
       </c>
       <c r="H77" t="n">
-        <v>0.06084325633212473</v>
+        <v>0.05392264582795181</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
         <v>9.31</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1381617248220258</v>
+        <v>0.125549990084949</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>44.27</v>
       </c>
       <c r="H79" t="n">
-        <v>0.2218554019884756</v>
+        <v>0.2134657721453238</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>43.96</v>
       </c>
       <c r="H80" t="n">
-        <v>0.06702522351186979</v>
+        <v>0.06063054736229601</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>13</v>
       </c>
       <c r="H81" t="n">
-        <v>0.04415769692836047</v>
+        <v>0.04535473167874637</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>8.98</v>
       </c>
       <c r="H82" t="n">
-        <v>0.1191614332426125</v>
+        <v>0.1187471105451149</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>7.68</v>
       </c>
       <c r="H83" t="n">
-        <v>0.1111655653980851</v>
+        <v>0.0944229415862532</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>31.42</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2299677739489984</v>
+        <v>0.2248321303043793</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>6.75</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0986306583560812</v>
+        <v>0.09345676512962242</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>1.01</v>
       </c>
       <c r="H86" t="n">
-        <v>0.08231463612392997</v>
+        <v>0.08314878229580835</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>9.73</v>
       </c>
       <c r="H87" t="n">
-        <v>0.22681539943214</v>
+        <v>0.2231486788862211</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>17.6</v>
       </c>
       <c r="H88" t="n">
-        <v>0.2289027109958885</v>
+        <v>0.2175086929512451</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>11.65</v>
       </c>
       <c r="H89" t="n">
-        <v>0.2182232155406898</v>
+        <v>0.210256443575917</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
         <v>12.49</v>
       </c>
       <c r="H90" t="n">
-        <v>0.1208847313562861</v>
+        <v>0.1170954522150438</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -3257,7 +3257,7 @@
         <v>4.77</v>
       </c>
       <c r="H91" t="n">
-        <v>0.06675547309627272</v>
+        <v>0.07537678830694394</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>13.67</v>
       </c>
       <c r="H92" t="n">
-        <v>0.09682287965743708</v>
+        <v>0.09773443560151296</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>39.14</v>
       </c>
       <c r="H93" t="n">
-        <v>0.08300885198851227</v>
+        <v>0.08333990455911633</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>174.78</v>
       </c>
       <c r="H94" t="n">
-        <v>0.03157350180175422</v>
+        <v>0.02401271698802732</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -3381,11 +3381,11 @@
         <v>4.63</v>
       </c>
       <c r="H95" t="n">
-        <v>-0.0001303697164966033</v>
+        <v>0.004689942772289957</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Suspicious</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
         <v>32.38</v>
       </c>
       <c r="H96" t="n">
-        <v>0.2198606348213246</v>
+        <v>0.2128463605228048</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         <v>11.76</v>
       </c>
       <c r="H97" t="n">
-        <v>0.2313001759220487</v>
+        <v>0.2252618250264231</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>5.36</v>
       </c>
       <c r="H98" t="n">
-        <v>0.1352292116151819</v>
+        <v>0.1252094052739591</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>45.7</v>
       </c>
       <c r="H99" t="n">
-        <v>0.1658200708345368</v>
+        <v>0.1688642656190211</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>23.87</v>
       </c>
       <c r="H100" t="n">
-        <v>0.2181972763239879</v>
+        <v>0.2121513037939401</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>16.57</v>
       </c>
       <c r="H101" t="n">
-        <v>0.2390524994665868</v>
+        <v>0.2280590921141127</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>15.36</v>
       </c>
       <c r="H102" t="n">
-        <v>0.114518838745408</v>
+        <v>0.1230232337292644</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>1.81</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1284873721988362</v>
+        <v>0.1250711051538251</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>3.51</v>
       </c>
       <c r="H104" t="n">
-        <v>0.03657557144410817</v>
+        <v>0.03353375473105158</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>7.82</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1446777071266722</v>
+        <v>0.13986534877808</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -3722,7 +3722,7 @@
         <v>33.75</v>
       </c>
       <c r="H106" t="n">
-        <v>0.1165255224781435</v>
+        <v>0.1167528038391726</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>67.56</v>
       </c>
       <c r="H107" t="n">
-        <v>0.09664172278052796</v>
+        <v>0.1019659581935515</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>3.3</v>
       </c>
       <c r="H108" t="n">
-        <v>-0.03408335057499334</v>
+        <v>-0.03199523453747555</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>47.73</v>
       </c>
       <c r="H109" t="n">
-        <v>0.1003481223757151</v>
+        <v>0.09995452544705763</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>22.23</v>
       </c>
       <c r="H110" t="n">
-        <v>0.2390736390390147</v>
+        <v>0.2306463122302268</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
         <v>17.13</v>
       </c>
       <c r="H111" t="n">
-        <v>0.1123531003068189</v>
+        <v>0.1180844601599906</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>7.58</v>
       </c>
       <c r="H112" t="n">
-        <v>0.06133109944593373</v>
+        <v>0.05319896333247265</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>23.21</v>
       </c>
       <c r="H113" t="n">
-        <v>0.1868159460180919</v>
+        <v>0.1890653839000958</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
         <v>7.45</v>
       </c>
       <c r="H114" t="n">
-        <v>0.2059333380777697</v>
+        <v>0.2025159520285448</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>5.9</v>
       </c>
       <c r="H115" t="n">
-        <v>0.1314053208101026</v>
+        <v>0.1221215951669701</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>42.96</v>
       </c>
       <c r="H116" t="n">
-        <v>0.1806541635107049</v>
+        <v>0.1733452104897895</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>31.22</v>
       </c>
       <c r="H117" t="n">
-        <v>0.1175071743571021</v>
+        <v>0.1042928019480274</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -4094,7 +4094,7 @@
         <v>33.12</v>
       </c>
       <c r="H118" t="n">
-        <v>0.06307550568257858</v>
+        <v>0.04954181572176397</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>2.79</v>
       </c>
       <c r="H119" t="n">
-        <v>0.1155692862544309</v>
+        <v>0.1067865308990954</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         <v>6.03</v>
       </c>
       <c r="H120" t="n">
-        <v>0.2077754621617236</v>
+        <v>0.1995700848258954</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>30.6</v>
       </c>
       <c r="H121" t="n">
-        <v>0.09609561095391328</v>
+        <v>0.09476224383473086</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>29.64</v>
       </c>
       <c r="H122" t="n">
-        <v>0.1312558020314785</v>
+        <v>0.1262033983879708</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>0.49</v>
       </c>
       <c r="H123" t="n">
-        <v>0.1128371021071608</v>
+        <v>0.1077782601397788</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>7.9</v>
       </c>
       <c r="H124" t="n">
-        <v>0.09576132001370363</v>
+        <v>0.09295638581864818</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>10.65</v>
       </c>
       <c r="H125" t="n">
-        <v>0.1169348000814938</v>
+        <v>0.1084629551655446</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>20.77</v>
       </c>
       <c r="H126" t="n">
-        <v>0.1179904133641809</v>
+        <v>0.1152693817741246</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>4.85</v>
       </c>
       <c r="H127" t="n">
-        <v>0.2153690071883986</v>
+        <v>0.2108265182653528</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>12.4</v>
       </c>
       <c r="H128" t="n">
-        <v>0.2202906218002723</v>
+        <v>0.2137993172848105</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>24.64</v>
       </c>
       <c r="H129" t="n">
-        <v>0.06881175482881585</v>
+        <v>0.05468996991302677</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>62.89</v>
       </c>
       <c r="H130" t="n">
-        <v>0.04023970931597443</v>
+        <v>0.04155615688249292</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -4497,7 +4497,7 @@
         <v>17.64</v>
       </c>
       <c r="H131" t="n">
-        <v>0.1057605557108739</v>
+        <v>0.09780816687183136</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         <v>36.41</v>
       </c>
       <c r="H132" t="n">
-        <v>0.10983119093135</v>
+        <v>0.1036628158538897</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>19.62</v>
       </c>
       <c r="H133" t="n">
-        <v>0.1602197954811407</v>
+        <v>0.168928688317424</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>19.06</v>
       </c>
       <c r="H134" t="n">
-        <v>0.1190223950224945</v>
+        <v>0.117221312896183</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
         <v>34.51</v>
       </c>
       <c r="H135" t="n">
-        <v>0.2078166728531617</v>
+        <v>0.2020349848766523</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>21.73</v>
       </c>
       <c r="H136" t="n">
-        <v>0.2264819305495508</v>
+        <v>0.2191902935989767</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>22.6</v>
       </c>
       <c r="H137" t="n">
-        <v>0.09868842130814826</v>
+        <v>0.08594857431166347</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>1.44</v>
       </c>
       <c r="H138" t="n">
-        <v>0.1256233410907179</v>
+        <v>0.1216500097186872</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>21.86</v>
       </c>
       <c r="H139" t="n">
-        <v>0.1942849812378767</v>
+        <v>0.1904810845946631</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>81.12</v>
       </c>
       <c r="H140" t="n">
-        <v>0.1448113483904977</v>
+        <v>0.13853654169522</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>28.14</v>
       </c>
       <c r="H141" t="n">
-        <v>0.1138687380871788</v>
+        <v>0.1174818499290804</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
         <v>18.91</v>
       </c>
       <c r="H142" t="n">
-        <v>0.1180945662013683</v>
+        <v>0.113202271723385</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         <v>33.84</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1116024821428147</v>
+        <v>0.1113781196721465</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         <v>66.64</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1839363290326314</v>
+        <v>0.1742756966446767</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>2.26</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2028195416431556</v>
+        <v>0.2051460961361173</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>17.99</v>
       </c>
       <c r="H146" t="n">
-        <v>0.2380734066984143</v>
+        <v>0.2297429925019018</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>2.21</v>
       </c>
       <c r="H147" t="n">
-        <v>0.1204493554299679</v>
+        <v>0.1163185624572773</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>2.45</v>
       </c>
       <c r="H148" t="n">
-        <v>0.0599892793737411</v>
+        <v>0.05333068952208342</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>89.23</v>
       </c>
       <c r="H149" t="n">
-        <v>0.1058896364738405</v>
+        <v>0.09556940270351821</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>23</v>
       </c>
       <c r="H150" t="n">
-        <v>0.1085694603476695</v>
+        <v>0.09839541482825642</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>8.24</v>
       </c>
       <c r="H151" t="n">
-        <v>0.1149138607912509</v>
+        <v>0.1100371339699124</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
         <v>12.87</v>
       </c>
       <c r="H152" t="n">
-        <v>0.2245585496886629</v>
+        <v>0.2145197045870186</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>11.35</v>
       </c>
       <c r="H153" t="n">
-        <v>0.1313773590834393</v>
+        <v>0.1262107779655292</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>22.72</v>
       </c>
       <c r="H154" t="n">
-        <v>0.2379527076574273</v>
+        <v>0.2298503094298261</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>31.18</v>
       </c>
       <c r="H155" t="n">
-        <v>0.2191621933305767</v>
+        <v>0.2137804173812638</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>41.03</v>
       </c>
       <c r="H156" t="n">
-        <v>0.2128518182700127</v>
+        <v>0.21055233835092</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>39.1</v>
       </c>
       <c r="H157" t="n">
-        <v>0.2043702448060635</v>
+        <v>0.1984167087797139</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>13.35</v>
       </c>
       <c r="H158" t="n">
-        <v>0.1451758810864341</v>
+        <v>0.1361030822257862</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>12.23</v>
       </c>
       <c r="H159" t="n">
-        <v>0.0944701479834037</v>
+        <v>0.09434913886880258</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>21.07</v>
       </c>
       <c r="H160" t="n">
-        <v>-0.04744583778115063</v>
+        <v>-0.04904465845248429</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
@@ -5427,7 +5427,7 @@
         <v>28.76</v>
       </c>
       <c r="H161" t="n">
-        <v>0.2212385504416041</v>
+        <v>0.2112606025416375</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>4.18</v>
       </c>
       <c r="H162" t="n">
-        <v>0.1112776205837613</v>
+        <v>0.1039408125096083</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>17.47</v>
       </c>
       <c r="H163" t="n">
-        <v>0.1440873571905649</v>
+        <v>0.1394503255475029</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>31.32</v>
       </c>
       <c r="H164" t="n">
-        <v>0.2197885428894084</v>
+        <v>0.2098534061568882</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>36.5</v>
       </c>
       <c r="H165" t="n">
-        <v>0.08668327158303113</v>
+        <v>0.09157800828280249</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>23.87</v>
       </c>
       <c r="H166" t="n">
-        <v>0.2272382912908172</v>
+        <v>0.2226701382319727</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
         <v>8.9</v>
       </c>
       <c r="H167" t="n">
-        <v>0.114050811158098</v>
+        <v>0.1135425347323179</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>10.88</v>
       </c>
       <c r="H168" t="n">
-        <v>0.03061189228628625</v>
+        <v>0.03089586570576619</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
         <v>29.18</v>
       </c>
       <c r="H169" t="n">
-        <v>0.2204791771093614</v>
+        <v>0.2182721714867536</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>168.36</v>
       </c>
       <c r="H170" t="n">
-        <v>0.0259852907723831</v>
+        <v>0.03579472622743796</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         <v>5.56</v>
       </c>
       <c r="H171" t="n">
-        <v>0.1969950255648316</v>
+        <v>0.1901698206143085</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>14.19</v>
       </c>
       <c r="H172" t="n">
-        <v>0.2225829594801096</v>
+        <v>0.2171006041241783</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>43.96</v>
       </c>
       <c r="H173" t="n">
-        <v>-0.03565506943187891</v>
+        <v>-0.04537646804660989</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
@@ -5830,7 +5830,7 @@
         <v>54.51</v>
       </c>
       <c r="H174" t="n">
-        <v>0.1968698039749136</v>
+        <v>0.1802145509584691</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>2.23</v>
       </c>
       <c r="H175" t="n">
-        <v>0.09322872078289446</v>
+        <v>0.08953573656126168</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>9.369999999999999</v>
       </c>
       <c r="H176" t="n">
-        <v>0.213434966551282</v>
+        <v>0.2048270453056114</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>157.69</v>
       </c>
       <c r="H177" t="n">
-        <v>-0.05578401096980112</v>
+        <v>-0.06186514706938462</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>2.83</v>
       </c>
       <c r="H178" t="n">
-        <v>0.121539201083675</v>
+        <v>0.1152174039455004</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>23.32</v>
       </c>
       <c r="H179" t="n">
-        <v>0.1539203622427274</v>
+        <v>0.1642579876140974</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>1.6</v>
       </c>
       <c r="H180" t="n">
-        <v>0.0553682612758204</v>
+        <v>0.05406739125818261</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>23.04</v>
       </c>
       <c r="H181" t="n">
-        <v>0.2185811267191218</v>
+        <v>0.2127322737838511</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>13.57</v>
       </c>
       <c r="H182" t="n">
-        <v>0.127477066837391</v>
+        <v>0.1230108700928086</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
@@ -6109,7 +6109,7 @@
         <v>46.33</v>
       </c>
       <c r="H183" t="n">
-        <v>0.1966177105030139</v>
+        <v>0.1917555629819394</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>31.19</v>
       </c>
       <c r="H184" t="n">
-        <v>0.2200234780479507</v>
+        <v>0.2098534061568882</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
@@ -6171,7 +6171,7 @@
         <v>4.57</v>
       </c>
       <c r="H185" t="n">
-        <v>0.1348164944879124</v>
+        <v>0.1289316361745203</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         <v>3.3</v>
       </c>
       <c r="H186" t="n">
-        <v>0.1661640275386376</v>
+        <v>0.170306690545732</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>53.31</v>
       </c>
       <c r="H187" t="n">
-        <v>0.07717508405603879</v>
+        <v>0.08289014924123095</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -6264,7 +6264,7 @@
         <v>20.55</v>
       </c>
       <c r="H188" t="n">
-        <v>0.1214052830698705</v>
+        <v>0.1168927251013999</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>6.36</v>
       </c>
       <c r="H189" t="n">
-        <v>0.1313892383051056</v>
+        <v>0.1233311820020871</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>20.61</v>
       </c>
       <c r="H190" t="n">
-        <v>0.09100201499051719</v>
+        <v>0.09427061465245634</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>16.31</v>
       </c>
       <c r="H191" t="n">
-        <v>0.1361410465678967</v>
+        <v>0.1476258297081418</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>19.15</v>
       </c>
       <c r="H192" t="n">
-        <v>0.2271388128325273</v>
+        <v>0.2226710168919908</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44.28</v>
       </c>
       <c r="H193" t="n">
-        <v>0.06595639653907992</v>
+        <v>0.06919534181417908</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>6.66</v>
       </c>
       <c r="H194" t="n">
-        <v>0.1394349864345064</v>
+        <v>0.1320521887401718</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>39.57</v>
       </c>
       <c r="H195" t="n">
-        <v>0.2174647166003426</v>
+        <v>0.206134339984321</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -6512,7 +6512,7 @@
         <v>55.55</v>
       </c>
       <c r="H196" t="n">
-        <v>0.2083375643433202</v>
+        <v>0.1969521670437948</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -6543,7 +6543,7 @@
         <v>22.53</v>
       </c>
       <c r="H197" t="n">
-        <v>0.1183841728777237</v>
+        <v>0.1031384067129035</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>9.279999999999999</v>
       </c>
       <c r="H198" t="n">
-        <v>0.06606219533342417</v>
+        <v>0.06841703735553151</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
         <v>3.95</v>
       </c>
       <c r="H199" t="n">
-        <v>0.05529587335693587</v>
+        <v>0.06277872342227153</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>8.1</v>
       </c>
       <c r="H200" t="n">
-        <v>0.1443705783341297</v>
+        <v>0.1411647486630702</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>25.52</v>
       </c>
       <c r="H201" t="n">
-        <v>0.2243881499459506</v>
+        <v>0.2195507524484359</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>15.32</v>
       </c>
       <c r="H202" t="n">
-        <v>0.1524951712165008</v>
+        <v>0.1494688140349965</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>43.31</v>
       </c>
       <c r="H203" t="n">
-        <v>0.2102014703112555</v>
+        <v>0.2042198697516462</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>4.88</v>
       </c>
       <c r="H204" t="n">
-        <v>0.1710119058910608</v>
+        <v>0.1739588394294887</v>
       </c>
       <c r="I204" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>38.16</v>
       </c>
       <c r="H205" t="n">
-        <v>-0.008476194260962355</v>
+        <v>-0.01836300830082449</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>121.46</v>
       </c>
       <c r="H206" t="n">
-        <v>0.08697482848478932</v>
+        <v>0.07651724255984804</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>17.77</v>
       </c>
       <c r="H207" t="n">
-        <v>0.07581110574615912</v>
+        <v>0.08714400614395934</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>13.51</v>
       </c>
       <c r="H208" t="n">
-        <v>0.1651150112285603</v>
+        <v>0.1753111387329984</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>10.98</v>
       </c>
       <c r="H209" t="n">
-        <v>0.1310153867999762</v>
+        <v>0.1308157170730762</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>24.8</v>
       </c>
       <c r="H210" t="n">
-        <v>0.2383310656865423</v>
+        <v>0.2302769245116644</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>3.15</v>
       </c>
       <c r="H211" t="n">
-        <v>0.07771424585386699</v>
+        <v>0.06976310797509033</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>97.70999999999999</v>
       </c>
       <c r="H212" t="n">
-        <v>0.1219008412218722</v>
+        <v>0.1082230475843017</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>10.78</v>
       </c>
       <c r="H213" t="n">
-        <v>0.0748275004834611</v>
+        <v>0.05907804640439152</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>26.03</v>
       </c>
       <c r="H214" t="n">
-        <v>0.1418614224190635</v>
+        <v>0.1351051475513864</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>10.29</v>
       </c>
       <c r="H215" t="n">
-        <v>0.09591852377900534</v>
+        <v>0.09225519477313071</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="H216" t="n">
-        <v>0.2093545574077093</v>
+        <v>0.206825040158949</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>74.34</v>
       </c>
       <c r="H217" t="n">
-        <v>0.08943656878094286</v>
+        <v>0.08926059852613866</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         <v>16.6</v>
       </c>
       <c r="H218" t="n">
-        <v>0.2200424510893802</v>
+        <v>0.2116592573065741</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>10.36</v>
       </c>
       <c r="H219" t="n">
-        <v>0.2115097039729965</v>
+        <v>0.2117548432676476</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>20.55</v>
       </c>
       <c r="H220" t="n">
-        <v>0.1214052830698705</v>
+        <v>0.1168927251013999</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>14.94</v>
       </c>
       <c r="H221" t="n">
-        <v>0.2256953164901823</v>
+        <v>0.2163104812002229</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         <v>14.13</v>
       </c>
       <c r="H222" t="n">
-        <v>0.1514149853234</v>
+        <v>0.149862191013666</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>23.25</v>
       </c>
       <c r="H223" t="n">
-        <v>0.2261314285450407</v>
+        <v>0.2192927145372581</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>36.73</v>
       </c>
       <c r="H224" t="n">
-        <v>0.2042771831991703</v>
+        <v>0.2012367610805106</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
@@ -7411,7 +7411,7 @@
         <v>13.78</v>
       </c>
       <c r="H225" t="n">
-        <v>0.119259714980879</v>
+        <v>0.1100421907686466</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>19.51</v>
       </c>
       <c r="H226" t="n">
-        <v>0.1346649114267187</v>
+        <v>0.147657570460524</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>11.59</v>
       </c>
       <c r="H227" t="n">
-        <v>0.1670933041259297</v>
+        <v>0.1654255670784736</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>33.99</v>
       </c>
       <c r="H228" t="n">
-        <v>0.2202480472350911</v>
+        <v>0.2124049785864046</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
@@ -7535,7 +7535,7 @@
         <v>14.24</v>
       </c>
       <c r="H229" t="n">
-        <v>0.2366231978710219</v>
+        <v>0.2278229113001324</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>10.53</v>
       </c>
       <c r="H230" t="n">
-        <v>0.1027286394744164</v>
+        <v>0.1018843007013548</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>23.47</v>
       </c>
       <c r="H231" t="n">
-        <v>0.2214651595739833</v>
+        <v>0.2160917849238998</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>2.28</v>
       </c>
       <c r="H232" t="n">
-        <v>0.1122788614261979</v>
+        <v>0.1073950871052016</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>29.16</v>
       </c>
       <c r="H233" t="n">
-        <v>0.2214904377152139</v>
+        <v>0.2136407165463157</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
@@ -7690,7 +7690,7 @@
         <v>17.68</v>
       </c>
       <c r="H234" t="n">
-        <v>0.1241207607128427</v>
+        <v>0.121440357112868</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>31.85</v>
       </c>
       <c r="H235" t="n">
-        <v>0.02405995097435587</v>
+        <v>0.01834979312973251</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         <v>11.55</v>
       </c>
       <c r="H236" t="n">
-        <v>0.2312139768202545</v>
+        <v>0.2252555329120856</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="H237" t="n">
-        <v>0.2117768645724525</v>
+        <v>0.2092190875640725</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>176.82</v>
       </c>
       <c r="H238" t="n">
-        <v>-0.07911600876157299</v>
+        <v>-0.08622009548248843</v>
       </c>
       <c r="I238" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>37.6</v>
       </c>
       <c r="H239" t="n">
-        <v>0.131068923112591</v>
+        <v>0.1272105509175582</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         <v>1.98</v>
       </c>
       <c r="H240" t="n">
-        <v>0.12548681514912</v>
+        <v>0.1235465282329425</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>28.34</v>
       </c>
       <c r="H241" t="n">
-        <v>0.2128328090999388</v>
+        <v>0.2105609806293128</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>13.98</v>
       </c>
       <c r="H242" t="n">
-        <v>0.1431436267696808</v>
+        <v>0.1448538854991857</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>2.05</v>
       </c>
       <c r="H243" t="n">
-        <v>0.1193464760342483</v>
+        <v>0.1121503153833368</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>13.31</v>
       </c>
       <c r="H244" t="n">
-        <v>0.08407224482914932</v>
+        <v>0.07766547209825458</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>8.92</v>
       </c>
       <c r="H245" t="n">
-        <v>0.08898345059120805</v>
+        <v>0.08682724083331728</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
@@ -8062,7 +8062,7 @@
         <v>12.62</v>
       </c>
       <c r="H246" t="n">
-        <v>0.09581281538518271</v>
+        <v>0.1007253361323971</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>19.79</v>
       </c>
       <c r="H247" t="n">
-        <v>0.06588997404410091</v>
+        <v>0.05372986968107241</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>94.55</v>
       </c>
       <c r="H248" t="n">
-        <v>0.1212635227783702</v>
+        <v>0.1202770901236458</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>28.54</v>
       </c>
       <c r="H249" t="n">
-        <v>0.1130129917409803</v>
+        <v>0.1155975197945265</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>3.23</v>
       </c>
       <c r="H250" t="n">
-        <v>0.05382982545876969</v>
+        <v>0.06046043181605643</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>29.27</v>
       </c>
       <c r="H251" t="n">
-        <v>0.07119943670747031</v>
+        <v>0.05624175290233446</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>10.73</v>
       </c>
       <c r="H252" t="n">
-        <v>0.1297673435531504</v>
+        <v>0.1258685399378233</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>12.66</v>
       </c>
       <c r="H253" t="n">
-        <v>0.04821172048923772</v>
+        <v>0.05042050384831853</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
         <v>38.35</v>
       </c>
       <c r="H254" t="n">
-        <v>0.2167489565700997</v>
+        <v>0.2091822992984994</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>17.89</v>
       </c>
       <c r="H255" t="n">
-        <v>0.2380734066984143</v>
+        <v>0.2293472093221041</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>11.41</v>
       </c>
       <c r="H256" t="n">
-        <v>0.1164902259807935</v>
+        <v>0.110055473380628</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>166.72</v>
       </c>
       <c r="H257" t="n">
-        <v>0.03553263319252609</v>
+        <v>0.02685944642448701</v>
       </c>
       <c r="I257" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>32.39</v>
       </c>
       <c r="H258" t="n">
-        <v>0.06623614092289754</v>
+        <v>0.05115641077868738</v>
       </c>
       <c r="I258" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         <v>20.9</v>
       </c>
       <c r="H259" t="n">
-        <v>0.2267255377398008</v>
+        <v>0.2195769512431107</v>
       </c>
       <c r="I259" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>25.55</v>
       </c>
       <c r="H260" t="n">
-        <v>0.192818248767461</v>
+        <v>0.1905867243042154</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>17.19</v>
       </c>
       <c r="H261" t="n">
-        <v>0.1549159570731654</v>
+        <v>0.1503714753760256</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
@@ -8558,7 +8558,7 @@
         <v>1.72</v>
       </c>
       <c r="H262" t="n">
-        <v>0.1200384900201724</v>
+        <v>0.1218677111910238</v>
       </c>
       <c r="I262" t="inlineStr">
         <is>
@@ -8589,7 +8589,7 @@
         <v>16.65</v>
       </c>
       <c r="H263" t="n">
-        <v>0.1524298950218981</v>
+        <v>0.1485765613479341</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>3.36</v>
       </c>
       <c r="H264" t="n">
-        <v>0.107814143632555</v>
+        <v>0.1110365399748592</v>
       </c>
       <c r="I264" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>52.21</v>
       </c>
       <c r="H265" t="n">
-        <v>0.2008826095961763</v>
+        <v>0.1932839415949945</v>
       </c>
       <c r="I265" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>6.11</v>
       </c>
       <c r="H266" t="n">
-        <v>0.1793652022430552</v>
+        <v>0.1729671412710227</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>15.97</v>
       </c>
       <c r="H267" t="n">
-        <v>0.2251400477081116</v>
+        <v>0.2184859046536991</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>13.39</v>
       </c>
       <c r="H268" t="n">
-        <v>0.221235796865047</v>
+        <v>0.2157758186855684</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>66.44</v>
       </c>
       <c r="H269" t="n">
-        <v>0.1732166711509151</v>
+        <v>0.1688628979391208</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         <v>50.66</v>
       </c>
       <c r="H270" t="n">
-        <v>0.20459907994731</v>
+        <v>0.194155478649125</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>1.19</v>
       </c>
       <c r="H271" t="n">
-        <v>0.01392278901764354</v>
+        <v>0.007049313013587022</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>22.59</v>
       </c>
       <c r="H272" t="n">
-        <v>0.2286849448710369</v>
+        <v>0.2168848695663606</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>1.35</v>
       </c>
       <c r="H273" t="n">
-        <v>-0.01343137187536392</v>
+        <v>-0.01707491695489916</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>4.64</v>
       </c>
       <c r="H274" t="n">
-        <v>0.0939666292387602</v>
+        <v>0.08215829783662654</v>
       </c>
       <c r="I274" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>37.7</v>
       </c>
       <c r="H275" t="n">
-        <v>0.1886333434979882</v>
+        <v>0.1802420007082454</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>22.8</v>
       </c>
       <c r="H276" t="n">
-        <v>0.05869674934747804</v>
+        <v>0.06576701781494598</v>
       </c>
       <c r="I276" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>28.16</v>
       </c>
       <c r="H277" t="n">
-        <v>0.1238210677540336</v>
+        <v>0.1140540775051025</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
@@ -9054,7 +9054,7 @@
         <v>13.08</v>
       </c>
       <c r="H278" t="n">
-        <v>0.1451365875733198</v>
+        <v>0.1362019587804581</v>
       </c>
       <c r="I278" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>5.08</v>
       </c>
       <c r="H279" t="n">
-        <v>0.1344669559224507</v>
+        <v>0.1285309210704755</v>
       </c>
       <c r="I279" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>38.39</v>
       </c>
       <c r="H280" t="n">
-        <v>0.2160697917149911</v>
+        <v>0.2126387641905496</v>
       </c>
       <c r="I280" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>15.44</v>
       </c>
       <c r="H281" t="n">
-        <v>0.2232733181317346</v>
+        <v>0.2185699974237057</v>
       </c>
       <c r="I281" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>10.21</v>
       </c>
       <c r="H282" t="n">
-        <v>0.1870388160586636</v>
+        <v>0.1896690763261327</v>
       </c>
       <c r="I282" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>12.72</v>
       </c>
       <c r="H283" t="n">
-        <v>0.2328030065405738</v>
+        <v>0.2282273186630541</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>14.76</v>
       </c>
       <c r="H284" t="n">
-        <v>0.1589359166249913</v>
+        <v>0.1524097339212577</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>16.5</v>
       </c>
       <c r="H285" t="n">
-        <v>0.1558494354529156</v>
+        <v>0.1504124462899665</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>29.75</v>
       </c>
       <c r="H286" t="n">
-        <v>0.2241795488246049</v>
+        <v>0.2097852695536306</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>11.56</v>
       </c>
       <c r="H287" t="n">
-        <v>0.1268757270329919</v>
+        <v>0.1463448826548195</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>21.01</v>
       </c>
       <c r="H288" t="n">
-        <v>0.1175095665342731</v>
+        <v>0.114038697864615</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>55.1</v>
       </c>
       <c r="H289" t="n">
-        <v>0.07234672992479985</v>
+        <v>0.06899579609080908</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>9.630000000000001</v>
       </c>
       <c r="H290" t="n">
-        <v>0.1640179766152107</v>
+        <v>0.1638405489206616</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>107.22</v>
       </c>
       <c r="H291" t="n">
-        <v>0.1060344270325114</v>
+        <v>0.09273217680325185</v>
       </c>
       <c r="I291" t="inlineStr">
         <is>
@@ -9488,7 +9488,7 @@
         <v>84.3</v>
       </c>
       <c r="H292" t="n">
-        <v>0.1470716727845224</v>
+        <v>0.1455958544197062</v>
       </c>
       <c r="I292" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>16.46</v>
       </c>
       <c r="H293" t="n">
-        <v>0.1635166358572933</v>
+        <v>0.1721615034882271</v>
       </c>
       <c r="I293" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>20.15</v>
       </c>
       <c r="H294" t="n">
-        <v>0.2286601587860084</v>
+        <v>0.2171141232691707</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
         <v>12.55</v>
       </c>
       <c r="H295" t="n">
-        <v>0.2233971393498565</v>
+        <v>0.2224637716643467</v>
       </c>
       <c r="I295" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>15.56</v>
       </c>
       <c r="H296" t="n">
-        <v>0.07045925342100223</v>
+        <v>0.06822300519247615</v>
       </c>
       <c r="I296" t="inlineStr">
         <is>
@@ -9643,7 +9643,7 @@
         <v>165.69</v>
       </c>
       <c r="H297" t="n">
-        <v>0.04062765300696458</v>
+        <v>0.03368890915594414</v>
       </c>
       <c r="I297" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>26.44</v>
       </c>
       <c r="H298" t="n">
-        <v>0.2234312164755619</v>
+        <v>0.2179440426387359</v>
       </c>
       <c r="I298" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>10.43</v>
       </c>
       <c r="H299" t="n">
-        <v>0.1274668512894511</v>
+        <v>0.1441792799614402</v>
       </c>
       <c r="I299" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>44.46</v>
       </c>
       <c r="H300" t="n">
-        <v>0.208760478853404</v>
+        <v>0.200081387819124</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>13.44</v>
       </c>
       <c r="H301" t="n">
-        <v>0.1580597598352147</v>
+        <v>0.1529440215685144</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>8.16</v>
       </c>
       <c r="H302" t="n">
-        <v>0.2176105334748038</v>
+        <v>0.2136397910535108</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>7.7</v>
       </c>
       <c r="H303" t="n">
-        <v>-0.03613011882664807</v>
+        <v>-0.03327469899772006</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>11.11</v>
       </c>
       <c r="H304" t="n">
-        <v>0.2207823483326368</v>
+        <v>0.2104114199354197</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
@@ -9891,7 +9891,7 @@
         <v>59.51</v>
       </c>
       <c r="H305" t="n">
-        <v>0.1915839798768179</v>
+        <v>0.1822677071849498</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>44.76</v>
       </c>
       <c r="H306" t="n">
-        <v>0.06612922796924603</v>
+        <v>0.05777441464919275</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>3.94</v>
       </c>
       <c r="H307" t="n">
-        <v>0.1349120863285886</v>
+        <v>0.128879078967599</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
@@ -9984,7 +9984,7 @@
         <v>49.66</v>
       </c>
       <c r="H308" t="n">
-        <v>0.2014436684875776</v>
+        <v>0.1898079031349901</v>
       </c>
       <c r="I308" t="inlineStr">
         <is>
@@ -10015,7 +10015,7 @@
         <v>8.710000000000001</v>
       </c>
       <c r="H309" t="n">
-        <v>0.1130201667777961</v>
+        <v>0.1065509187416144</v>
       </c>
       <c r="I309" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>0.15</v>
       </c>
       <c r="H310" t="n">
-        <v>0.173531128683427</v>
+        <v>0.1809542466446974</v>
       </c>
       <c r="I310" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>8.19</v>
       </c>
       <c r="H311" t="n">
-        <v>0.1150254804600638</v>
+        <v>0.1060092404460991</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>25.2</v>
       </c>
       <c r="H312" t="n">
-        <v>0.2164727637855</v>
+        <v>0.2129021400471023</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>2.82</v>
       </c>
       <c r="H313" t="n">
-        <v>-0.03017279756998947</v>
+        <v>-0.04113217372791234</v>
       </c>
       <c r="I313" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>11.82</v>
       </c>
       <c r="H314" t="n">
-        <v>0.2317344039365282</v>
+        <v>0.2252618250264231</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>32.87</v>
       </c>
       <c r="H315" t="n">
-        <v>0.1096580784737334</v>
+        <v>0.1110695368599315</v>
       </c>
       <c r="I315" t="inlineStr">
         <is>
@@ -10232,7 +10232,7 @@
         <v>8.17</v>
       </c>
       <c r="H316" t="n">
-        <v>-0.008978801891247334</v>
+        <v>-0.005071649655945532</v>
       </c>
       <c r="I316" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>29.82</v>
       </c>
       <c r="H317" t="n">
-        <v>0.2199018247922695</v>
+        <v>0.2091787108928475</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         <v>47.98</v>
       </c>
       <c r="H318" t="n">
-        <v>0.1130709889352201</v>
+        <v>0.1244854731070496</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>61.98</v>
       </c>
       <c r="H319" t="n">
-        <v>0.1701199840883312</v>
+        <v>0.1594029531215939</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         <v>5.86</v>
       </c>
       <c r="H320" t="n">
-        <v>0.1241014810671649</v>
+        <v>0.134903814494132</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>8.960000000000001</v>
       </c>
       <c r="H321" t="n">
-        <v>0.1797628580667304</v>
+        <v>0.1834676378797852</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>14.62</v>
       </c>
       <c r="H322" t="n">
-        <v>0.1312475738768655</v>
+        <v>0.1262456375944199</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>2.28</v>
       </c>
       <c r="H323" t="n">
-        <v>0.02111100639413654</v>
+        <v>0.02417019617994354</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         <v>6.05</v>
       </c>
       <c r="H324" t="n">
-        <v>0.1317710065921095</v>
+        <v>0.123924596246892</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>55.17</v>
       </c>
       <c r="H325" t="n">
-        <v>0.1814557990452825</v>
+        <v>0.1721547458275944</v>
       </c>
       <c r="I325" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>23.78</v>
       </c>
       <c r="H326" t="n">
-        <v>0.1119200380034027</v>
+        <v>0.1092278333414071</v>
       </c>
       <c r="I326" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>16.98</v>
       </c>
       <c r="H327" t="n">
-        <v>-0.001891524584959448</v>
+        <v>-0.01512801250606355</v>
       </c>
       <c r="I327" t="inlineStr">
         <is>
@@ -10604,7 +10604,7 @@
         <v>27.09</v>
       </c>
       <c r="H328" t="n">
-        <v>0.08163359350970922</v>
+        <v>0.08630797826201209</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>6.95</v>
       </c>
       <c r="H329" t="n">
-        <v>-0.01866434429789277</v>
+        <v>-0.01920765666272417</v>
       </c>
       <c r="I329" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>5.47</v>
       </c>
       <c r="H330" t="n">
-        <v>0.1970391538218479</v>
+        <v>0.1861578743486305</v>
       </c>
       <c r="I330" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>15</v>
       </c>
       <c r="H331" t="n">
-        <v>0.2177719773946797</v>
+        <v>0.2116196677399546</v>
       </c>
       <c r="I331" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>60.49</v>
       </c>
       <c r="H332" t="n">
-        <v>0.1914254085409981</v>
+        <v>0.1800263555807465</v>
       </c>
       <c r="I332" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>27.68</v>
       </c>
       <c r="H333" t="n">
-        <v>0.2231371620939208</v>
+        <v>0.216641019568749</v>
       </c>
       <c r="I333" t="inlineStr">
         <is>
@@ -10790,7 +10790,7 @@
         <v>28.98</v>
       </c>
       <c r="H334" t="n">
-        <v>0.2331446479779378</v>
+        <v>0.2279014206369904</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>150.92</v>
       </c>
       <c r="H335" t="n">
-        <v>-0.03780971538243416</v>
+        <v>-0.03194555303877866</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>1.16</v>
       </c>
       <c r="H336" t="n">
-        <v>0.04950789455791083</v>
+        <v>0.04957373504271501</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>13.28</v>
       </c>
       <c r="H337" t="n">
-        <v>0.2125596606677144</v>
+        <v>0.2094078961087759</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>22.49</v>
       </c>
       <c r="H338" t="n">
-        <v>0.1036645364146278</v>
+        <v>0.09286863475934426</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>15.33</v>
       </c>
       <c r="H339" t="n">
-        <v>0.2233394962375828</v>
+        <v>0.2184262921173055</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>8.51</v>
       </c>
       <c r="H340" t="n">
-        <v>0.2245752765911033</v>
+        <v>0.2219291329879556</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
@@ -11007,7 +11007,7 @@
         <v>9.710000000000001</v>
       </c>
       <c r="H341" t="n">
-        <v>0.2069471194300653</v>
+        <v>0.1997980606811399</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>43.83</v>
       </c>
       <c r="H342" t="n">
-        <v>0.1235737909311955</v>
+        <v>0.1156869925732754</v>
       </c>
       <c r="I342" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>127.62</v>
       </c>
       <c r="H343" t="n">
-        <v>0.0683633426159217</v>
+        <v>0.06879358847451589</v>
       </c>
       <c r="I343" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>34.08</v>
       </c>
       <c r="H344" t="n">
-        <v>0.1037541121132536</v>
+        <v>0.09566953289467051</v>
       </c>
       <c r="I344" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         <v>29.08</v>
       </c>
       <c r="H345" t="n">
-        <v>0.2331446479779378</v>
+        <v>0.2275917355666082</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>10.04</v>
       </c>
       <c r="H346" t="n">
-        <v>0.1141555667747177</v>
+        <v>0.1092175493400979</v>
       </c>
       <c r="I346" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>11.29</v>
       </c>
       <c r="H347" t="n">
-        <v>0.2207823483326368</v>
+        <v>0.210923762577767</v>
       </c>
       <c r="I347" t="inlineStr">
         <is>
@@ -11224,7 +11224,7 @@
         <v>37.74</v>
       </c>
       <c r="H348" t="n">
-        <v>0.2163206490429585</v>
+        <v>0.2125101114036315</v>
       </c>
       <c r="I348" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>48.49</v>
       </c>
       <c r="H349" t="n">
-        <v>0.2141100618559296</v>
+        <v>0.2099655837507691</v>
       </c>
       <c r="I349" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>7.22</v>
       </c>
       <c r="H350" t="n">
-        <v>0.1252334322000656</v>
+        <v>0.1200945576295196</v>
       </c>
       <c r="I350" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>6.15</v>
       </c>
       <c r="H351" t="n">
-        <v>0.2076009950240174</v>
+        <v>0.1994238159059663</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>9.359999999999999</v>
       </c>
       <c r="H352" t="n">
-        <v>0.1389313536247885</v>
+        <v>0.1413152340545404</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>8.67</v>
       </c>
       <c r="H353" t="n">
-        <v>0.1311981906100304</v>
+        <v>0.1291185214901225</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>1.74</v>
       </c>
       <c r="H354" t="n">
-        <v>0.1191664135500677</v>
+        <v>0.1122625403732778</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
@@ -11441,7 +11441,7 @@
         <v>17.53</v>
       </c>
       <c r="H355" t="n">
-        <v>-0.03392830391946822</v>
+        <v>-0.02798475024155311</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>36.32</v>
       </c>
       <c r="H356" t="n">
-        <v>0.06563676071083147</v>
+        <v>0.08309022316561143</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>6.32</v>
       </c>
       <c r="H357" t="n">
-        <v>0.09167057320197125</v>
+        <v>0.0811424346271562</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
@@ -11534,7 +11534,7 @@
         <v>5.56</v>
       </c>
       <c r="H358" t="n">
-        <v>0.1221476877385267</v>
+        <v>0.1117644815240149</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>17.42</v>
       </c>
       <c r="H359" t="n">
-        <v>0.2255525492824522</v>
+        <v>0.219704899571004</v>
       </c>
       <c r="I359" t="inlineStr">
         <is>
@@ -11596,7 +11596,7 @@
         <v>7.76</v>
       </c>
       <c r="H360" t="n">
-        <v>0.1420118254050952</v>
+        <v>0.1331458038406999</v>
       </c>
       <c r="I360" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>17.36</v>
       </c>
       <c r="H361" t="n">
-        <v>0.2223524555937958</v>
+        <v>0.2175577977334505</v>
       </c>
       <c r="I361" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>18.81</v>
       </c>
       <c r="H362" t="n">
-        <v>0.1295458624660555</v>
+        <v>0.1184923062119345</v>
       </c>
       <c r="I362" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>56.52</v>
       </c>
       <c r="H363" t="n">
-        <v>0.1919391657779249</v>
+        <v>0.1779208836268711</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>24.32</v>
       </c>
       <c r="H364" t="n">
-        <v>0.2389737274096765</v>
+        <v>0.2289138917311257</v>
       </c>
       <c r="I364" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>23.66</v>
       </c>
       <c r="H365" t="n">
-        <v>0.2295079714626996</v>
+        <v>0.2161916739594303</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>0.99</v>
       </c>
       <c r="H366" t="n">
-        <v>0.05356054134584143</v>
+        <v>0.0502207557227704</v>
       </c>
       <c r="I366" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>30.78</v>
       </c>
       <c r="H367" t="n">
-        <v>0.2185945912357699</v>
+        <v>0.2140372264265521</v>
       </c>
       <c r="I367" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>59.42</v>
       </c>
       <c r="H368" t="n">
-        <v>0.1872883663970181</v>
+        <v>0.1763014883548104</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>13.38</v>
       </c>
       <c r="H369" t="n">
-        <v>0.1517389454779531</v>
+        <v>0.1487795113134567</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>19.52</v>
       </c>
       <c r="H370" t="n">
-        <v>0.2279286678259131</v>
+        <v>0.2236233810082547</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>16.45</v>
       </c>
       <c r="H371" t="n">
-        <v>0.1890987318185415</v>
+        <v>0.1905892041843523</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>6.91</v>
       </c>
       <c r="H372" t="n">
-        <v>0.1191188728469076</v>
+        <v>0.1124779614106054</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>2.59</v>
       </c>
       <c r="H373" t="n">
-        <v>0.1642208191148813</v>
+        <v>0.1682566220616489</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -12030,7 +12030,7 @@
         <v>9.470000000000001</v>
       </c>
       <c r="H374" t="n">
-        <v>0.1006977284025375</v>
+        <v>0.09681464417337848</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>18.8</v>
       </c>
       <c r="H375" t="n">
-        <v>0.2278661394103904</v>
+        <v>0.2180024696294068</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>22.29</v>
       </c>
       <c r="H376" t="n">
-        <v>0.1146124363631736</v>
+        <v>0.1119091483722234</v>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>26.32</v>
       </c>
       <c r="H377" t="n">
-        <v>0.1122910337520735</v>
+        <v>0.099101307431258</v>
       </c>
       <c r="I377" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>9.59</v>
       </c>
       <c r="H378" t="n">
-        <v>0.2169279629629566</v>
+        <v>0.2073418510139329</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>22.44</v>
       </c>
       <c r="H379" t="n">
-        <v>0.2184942359776214</v>
+        <v>0.2127632824114293</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>18.46</v>
       </c>
       <c r="H380" t="n">
-        <v>0.2254513004761659</v>
+        <v>0.2195235283955542</v>
       </c>
       <c r="I380" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         <v>7.42</v>
       </c>
       <c r="H381" t="n">
-        <v>0.2253183124827359</v>
+        <v>0.2192133507626476</v>
       </c>
       <c r="I381" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>48.21</v>
       </c>
       <c r="H382" t="n">
-        <v>0.2142924727740336</v>
+        <v>0.2106626313923576</v>
       </c>
       <c r="I382" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="H383" t="n">
-        <v>0.1432948664261178</v>
+        <v>0.1474963336056537</v>
       </c>
       <c r="I383" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>4.57</v>
       </c>
       <c r="H384" t="n">
-        <v>0.09991823356500684</v>
+        <v>0.09775512036517886</v>
       </c>
       <c r="I384" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>23.57</v>
       </c>
       <c r="H385" t="n">
-        <v>0.1924107571640813</v>
+        <v>0.1902124626136619</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>5.14</v>
       </c>
       <c r="H386" t="n">
-        <v>0.1942694877070519</v>
+        <v>0.1900425442561179</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         <v>10.95</v>
       </c>
       <c r="H387" t="n">
-        <v>0.04305626156182862</v>
+        <v>0.0393280126164437</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>28.81</v>
       </c>
       <c r="H388" t="n">
-        <v>0.05667568125624989</v>
+        <v>0.03996485966511376</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
@@ -12495,7 +12495,7 @@
         <v>4.53</v>
       </c>
       <c r="H389" t="n">
-        <v>0.2158712677856583</v>
+        <v>0.2127162786923403</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>23.71</v>
       </c>
       <c r="H390" t="n">
-        <v>0.1287284035968121</v>
+        <v>0.1230432520752248</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -12557,7 +12557,7 @@
         <v>24.58</v>
       </c>
       <c r="H391" t="n">
-        <v>0.2221858019355245</v>
+        <v>0.2163077097457717</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>41.12</v>
       </c>
       <c r="H392" t="n">
-        <v>0.2129359662524719</v>
+        <v>0.2061005249831408</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>29.13</v>
       </c>
       <c r="H393" t="n">
-        <v>0.05752658998348503</v>
+        <v>0.06469562038706067</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -12650,7 +12650,7 @@
         <v>10.61</v>
       </c>
       <c r="H394" t="n">
-        <v>0.164292215562565</v>
+        <v>0.1664208245754663</v>
       </c>
       <c r="I394" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>15.23</v>
       </c>
       <c r="H395" t="n">
-        <v>0.2212108062982713</v>
+        <v>0.216520095173677</v>
       </c>
       <c r="I395" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>27.1</v>
       </c>
       <c r="H396" t="n">
-        <v>-0.01500759583971212</v>
+        <v>-0.02390997630407343</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>3.78</v>
       </c>
       <c r="H397" t="n">
-        <v>0.04705718128673342</v>
+        <v>0.04793651719961145</v>
       </c>
       <c r="I397" t="inlineStr">
         <is>
@@ -12774,7 +12774,7 @@
         <v>5.86</v>
       </c>
       <c r="H398" t="n">
-        <v>0.1310837227744255</v>
+        <v>0.1196839936498855</v>
       </c>
       <c r="I398" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>9.33</v>
       </c>
       <c r="H399" t="n">
-        <v>0.1642567050279854</v>
+        <v>0.1631269379194493</v>
       </c>
       <c r="I399" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>5.68</v>
       </c>
       <c r="H400" t="n">
-        <v>0.200998769376198</v>
+        <v>0.1919620487278403</v>
       </c>
       <c r="I400" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>7.02</v>
       </c>
       <c r="H401" t="n">
-        <v>0.204254835851185</v>
+        <v>0.2023051074272144</v>
       </c>
       <c r="I401" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>7.27</v>
       </c>
       <c r="H402" t="n">
-        <v>0.1271638314144411</v>
+        <v>0.1379834908572311</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
@@ -12929,7 +12929,7 @@
         <v>17.25</v>
       </c>
       <c r="H403" t="n">
-        <v>0.2257147884520606</v>
+        <v>0.2198443086994775</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>11.84</v>
       </c>
       <c r="H404" t="n">
-        <v>0.1510426467707597</v>
+        <v>0.1449061483803057</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>8.17</v>
       </c>
       <c r="H405" t="n">
-        <v>0.08293818127564434</v>
+        <v>0.0785137861871199</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>17.52</v>
       </c>
       <c r="H406" t="n">
-        <v>0.05211002580460711</v>
+        <v>0.04448143862169707</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>15.05</v>
       </c>
       <c r="H407" t="n">
-        <v>0.1444306024114637</v>
+        <v>0.1336243389136329</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>26.21</v>
       </c>
       <c r="H408" t="n">
-        <v>-0.05024177133540841</v>
+        <v>-0.05042815514158494</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>0.45</v>
       </c>
       <c r="H409" t="n">
-        <v>0.0440191960187909</v>
+        <v>0.04637240880977311</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         <v>14.3</v>
       </c>
       <c r="H410" t="n">
-        <v>0.10011777853732</v>
+        <v>0.08955700752350648</v>
       </c>
       <c r="I410" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>12.1</v>
       </c>
       <c r="H411" t="n">
-        <v>0.06501947459251811</v>
+        <v>0.058183582550976</v>
       </c>
       <c r="I411" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>28.85</v>
       </c>
       <c r="H412" t="n">
-        <v>0.2338190661049352</v>
+        <v>0.2279014206369904</v>
       </c>
       <c r="I412" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>74.40000000000001</v>
       </c>
       <c r="H413" t="n">
-        <v>0.1605306368234415</v>
+        <v>0.1546216373019518</v>
       </c>
       <c r="I413" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>17.43</v>
       </c>
       <c r="H414" t="n">
-        <v>0.196519771138798</v>
+        <v>0.1918630102354185</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>54.68</v>
       </c>
       <c r="H415" t="n">
-        <v>0.1992352554196545</v>
+        <v>0.1857779570439365</v>
       </c>
       <c r="I415" t="inlineStr">
         <is>
@@ -13332,7 +13332,7 @@
         <v>32.65</v>
       </c>
       <c r="H416" t="n">
-        <v>0.048169456377536</v>
+        <v>0.03947999184910067</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
@@ -13363,7 +13363,7 @@
         <v>3.25</v>
       </c>
       <c r="H417" t="n">
-        <v>0.1175915001374666</v>
+        <v>0.1083820565563403</v>
       </c>
       <c r="I417" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>11.12</v>
       </c>
       <c r="H418" t="n">
-        <v>0.2309158043116795</v>
+        <v>0.2253413471402033</v>
       </c>
       <c r="I418" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>8.109999999999999</v>
       </c>
       <c r="H419" t="n">
-        <v>0.2254679711488292</v>
+        <v>0.2218212772224305</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>14.63</v>
       </c>
       <c r="H420" t="n">
-        <v>0.2202158099065438</v>
+        <v>0.216278673127828</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>3.5</v>
       </c>
       <c r="H421" t="n">
-        <v>0.126596929067739</v>
+        <v>0.1263999551773616</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>73.20999999999999</v>
       </c>
       <c r="H422" t="n">
-        <v>0.1718184336151493</v>
+        <v>0.1562334466433955</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>25.19</v>
       </c>
       <c r="H423" t="n">
-        <v>0.06964425349084979</v>
+        <v>0.05508035009913836</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>12.41</v>
       </c>
       <c r="H424" t="n">
-        <v>0.2324218475746171</v>
+        <v>0.2271888169716121</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>1.28</v>
       </c>
       <c r="H425" t="n">
-        <v>0.1778094967143967</v>
+        <v>0.1749534350114569</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
@@ -13642,7 +13642,7 @@
         <v>3.86</v>
       </c>
       <c r="H426" t="n">
-        <v>0.05610197531613326</v>
+        <v>0.05752680063368687</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>9.42</v>
       </c>
       <c r="H427" t="n">
-        <v>0.1361242852974732</v>
+        <v>0.1330535281150418</v>
       </c>
       <c r="I427" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>27.16</v>
       </c>
       <c r="H428" t="n">
-        <v>0.1838376778108029</v>
+        <v>0.1839341854935034</v>
       </c>
       <c r="I428" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>9.73</v>
       </c>
       <c r="H429" t="n">
-        <v>0.1147878462213883</v>
+        <v>0.1143920958950994</v>
       </c>
       <c r="I429" t="inlineStr">
         <is>
@@ -13766,7 +13766,7 @@
         <v>53.99</v>
       </c>
       <c r="H430" t="n">
-        <v>0.09458070021101328</v>
+        <v>0.08053113111925581</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>3.3</v>
       </c>
       <c r="H431" t="n">
-        <v>0.1177042199505599</v>
+        <v>0.1083820565563403</v>
       </c>
       <c r="I431" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>46.87</v>
       </c>
       <c r="H432" t="n">
-        <v>0.2161200618948472</v>
+        <v>0.2124207288593418</v>
       </c>
       <c r="I432" t="inlineStr">
         <is>
@@ -13859,11 +13859,11 @@
         <v>3.35</v>
       </c>
       <c r="H433" t="n">
-        <v>3.726013539040451e-06</v>
+        <v>-0.003976244397271178</v>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Suspicious</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
         <v>17.63</v>
       </c>
       <c r="H434" t="n">
-        <v>0.09216196464830262</v>
+        <v>0.09395639200191452</v>
       </c>
       <c r="I434" t="inlineStr">
         <is>
@@ -13921,7 +13921,7 @@
         <v>10.92</v>
       </c>
       <c r="H435" t="n">
-        <v>0.2210502484153931</v>
+        <v>0.219886659844118</v>
       </c>
       <c r="I435" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>25.61</v>
       </c>
       <c r="H436" t="n">
-        <v>0.1078364825091993</v>
+        <v>0.1061643338332442</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>16.03</v>
       </c>
       <c r="H437" t="n">
-        <v>0.2251400477081116</v>
+        <v>0.2184859046536991</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
@@ -14014,7 +14014,7 @@
         <v>55.76</v>
       </c>
       <c r="H438" t="n">
-        <v>0.2042615439736749</v>
+        <v>0.1963347075427969</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>36.52</v>
       </c>
       <c r="H439" t="n">
-        <v>0.2198369802698639</v>
+        <v>0.2106921803241353</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>123.84</v>
       </c>
       <c r="H440" t="n">
-        <v>-0.06854443297584889</v>
+        <v>-0.07283483578055117</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>5.68</v>
       </c>
       <c r="H441" t="n">
-        <v>0.1580493911224918</v>
+        <v>0.1580505284263759</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
@@ -14138,7 +14138,7 @@
         <v>2.07</v>
       </c>
       <c r="H442" t="n">
-        <v>0.1014614688290232</v>
+        <v>0.09732274972679678</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>17.44</v>
       </c>
       <c r="H443" t="n">
-        <v>0.2255525492824522</v>
+        <v>0.219704899571004</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>36.34</v>
       </c>
       <c r="H444" t="n">
-        <v>0.2141491260365057</v>
+        <v>0.2113283497715088</v>
       </c>
       <c r="I444" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>15.76</v>
       </c>
       <c r="H445" t="n">
-        <v>0.1356644108955116</v>
+        <v>0.1425336476605157</v>
       </c>
       <c r="I445" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>19.18</v>
       </c>
       <c r="H446" t="n">
-        <v>0.045541924391445</v>
+        <v>0.05625242311906609</v>
       </c>
       <c r="I446" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>58.84</v>
       </c>
       <c r="H447" t="n">
-        <v>0.02392286750433992</v>
+        <v>0.01601025218653951</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>16.46</v>
       </c>
       <c r="H448" t="n">
-        <v>0.1354827615066284</v>
+        <v>0.1286064367517792</v>
       </c>
       <c r="I448" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>1.59</v>
       </c>
       <c r="H449" t="n">
-        <v>0.08477616382273423</v>
+        <v>0.07082582131064086</v>
       </c>
       <c r="I449" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>19.21</v>
       </c>
       <c r="H450" t="n">
-        <v>0.1349403122822007</v>
+        <v>0.123180887200075</v>
       </c>
       <c r="I450" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>81.34999999999999</v>
       </c>
       <c r="H451" t="n">
-        <v>0.1548743322256242</v>
+        <v>0.1516093584629558</v>
       </c>
       <c r="I451" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>43.02</v>
       </c>
       <c r="H452" t="n">
-        <v>0.2100221995832451</v>
+        <v>0.2027964320743448</v>
       </c>
       <c r="I452" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>15.09</v>
       </c>
       <c r="H453" t="n">
-        <v>0.1317337099015224</v>
+        <v>0.1258411960265774</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>1.8</v>
       </c>
       <c r="H454" t="n">
-        <v>0.03762001939691673</v>
+        <v>0.02543451748755088</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>19.02</v>
       </c>
       <c r="H455" t="n">
-        <v>0.2258704847464479</v>
+        <v>0.2196336915643304</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>3.15</v>
       </c>
       <c r="H456" t="n">
-        <v>0.1032667311458145</v>
+        <v>0.1029941341034942</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>4.8</v>
       </c>
       <c r="H457" t="n">
-        <v>0.09225532594796892</v>
+        <v>0.0914795193068112</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>30.36</v>
       </c>
       <c r="H458" t="n">
-        <v>0.2322191087065419</v>
+        <v>0.2255568425003666</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>3.33</v>
       </c>
       <c r="H459" t="n">
-        <v>0.21138668276249</v>
+        <v>0.2098931918085561</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
@@ -14696,7 +14696,7 @@
         <v>16.71</v>
       </c>
       <c r="H460" t="n">
-        <v>0.2287809689898246</v>
+        <v>0.2226559684998911</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
@@ -14727,7 +14727,7 @@
         <v>6.64</v>
       </c>
       <c r="H461" t="n">
-        <v>0.1781334356999592</v>
+        <v>0.1796857776488188</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>4.21</v>
       </c>
       <c r="H462" t="n">
-        <v>0.07925558804985666</v>
+        <v>0.07384582414381458</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
@@ -14789,7 +14789,7 @@
         <v>12.53</v>
       </c>
       <c r="H463" t="n">
-        <v>0.1315427445455836</v>
+        <v>0.1289151216663559</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>102.82</v>
       </c>
       <c r="H464" t="n">
-        <v>-0.01896357835779772</v>
+        <v>-0.03355918671815961</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>5.3</v>
       </c>
       <c r="H465" t="n">
-        <v>0.1197594641795007</v>
+        <v>0.1182383305262178</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
@@ -14882,7 +14882,7 @@
         <v>8.859999999999999</v>
       </c>
       <c r="H466" t="n">
-        <v>0.1386725655521444</v>
+        <v>0.1411621441809266</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>5.1</v>
       </c>
       <c r="H467" t="n">
-        <v>0.2163340310171514</v>
+        <v>0.2122682190383783</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>34.3</v>
       </c>
       <c r="H468" t="n">
-        <v>0.08411819756919869</v>
+        <v>0.07914980289111551</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>37.83</v>
       </c>
       <c r="H469" t="n">
-        <v>0.2202360728909687</v>
+        <v>0.2084351228810757</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>13.47</v>
       </c>
       <c r="H470" t="n">
-        <v>-0.04400251017686807</v>
+        <v>-0.0448770149491341</v>
       </c>
       <c r="I470" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>155.07</v>
       </c>
       <c r="H471" t="n">
-        <v>-0.01409376759758418</v>
+        <v>-0.01786113011878609</v>
       </c>
       <c r="I471" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>31.13</v>
       </c>
       <c r="H472" t="n">
-        <v>0.2302651507205871</v>
+        <v>0.2234712541551665</v>
       </c>
       <c r="I472" t="inlineStr">
         <is>
@@ -15099,11 +15099,11 @@
         <v>16.82</v>
       </c>
       <c r="H473" t="n">
-        <v>0.001030089059228523</v>
+        <v>-0.01032517305386982</v>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Suspicious</t>
         </is>
       </c>
     </row>
@@ -15130,7 +15130,7 @@
         <v>2.02</v>
       </c>
       <c r="H474" t="n">
-        <v>0.1168287052357436</v>
+        <v>0.1151526035414986</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>20.95</v>
       </c>
       <c r="H475" t="n">
-        <v>0.2280835475296739</v>
+        <v>0.2170505085902912</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>2.97</v>
       </c>
       <c r="H476" t="n">
-        <v>0.1266306105899281</v>
+        <v>0.1186177610027621</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>6.72</v>
       </c>
       <c r="H477" t="n">
-        <v>0.08357117759001009</v>
+        <v>0.08807020240824814</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>7.31</v>
       </c>
       <c r="H478" t="n">
-        <v>0.07345995566723951</v>
+        <v>0.06757418183489206</v>
       </c>
       <c r="I478" t="inlineStr">
         <is>
@@ -15285,7 +15285,7 @@
         <v>9.32</v>
       </c>
       <c r="H479" t="n">
-        <v>0.07824733890715529</v>
+        <v>0.07063379958231597</v>
       </c>
       <c r="I479" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
         <v>5.19</v>
       </c>
       <c r="H480" t="n">
-        <v>0.1248208356323548</v>
+        <v>0.1190849005014297</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>6.23</v>
       </c>
       <c r="H481" t="n">
-        <v>0.1409924531090304</v>
+        <v>0.1388129988373376</v>
       </c>
       <c r="I481" t="inlineStr">
         <is>
@@ -15378,7 +15378,7 @@
         <v>2.94</v>
       </c>
       <c r="H482" t="n">
-        <v>0.06670174521882066</v>
+        <v>0.04575663210796599</v>
       </c>
       <c r="I482" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>11.74</v>
       </c>
       <c r="H483" t="n">
-        <v>0.1024484617342201</v>
+        <v>0.09300489245272969</v>
       </c>
       <c r="I483" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>5.75</v>
       </c>
       <c r="H484" t="n">
-        <v>0.09453875958453994</v>
+        <v>0.09283888030736398</v>
       </c>
       <c r="I484" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>11.57</v>
       </c>
       <c r="H485" t="n">
-        <v>0.144041498071222</v>
+        <v>0.1355792312632146</v>
       </c>
       <c r="I485" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>26.02</v>
       </c>
       <c r="H486" t="n">
-        <v>0.2234312164755619</v>
+        <v>0.2180000823853528</v>
       </c>
       <c r="I486" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>34.37</v>
       </c>
       <c r="H487" t="n">
-        <v>0.08798919166569252</v>
+        <v>0.08330823683672206</v>
       </c>
       <c r="I487" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>10.79</v>
       </c>
       <c r="H488" t="n">
-        <v>0.2091112622216496</v>
+        <v>0.2040805051802612</v>
       </c>
       <c r="I488" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>7.8</v>
       </c>
       <c r="H489" t="n">
-        <v>0.08581747133845541</v>
+        <v>0.08103331947168413</v>
       </c>
       <c r="I489" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>42.71</v>
       </c>
       <c r="H490" t="n">
-        <v>0.2105279566784033</v>
+        <v>0.2100473956474063</v>
       </c>
       <c r="I490" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>50.5</v>
       </c>
       <c r="H491" t="n">
-        <v>0.2028346447795356</v>
+        <v>0.1956373930765513</v>
       </c>
       <c r="I491" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>33.4</v>
       </c>
       <c r="H492" t="n">
-        <v>0.2295559458952571</v>
+        <v>0.2256608810315625</v>
       </c>
       <c r="I492" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>49.58</v>
       </c>
       <c r="H493" t="n">
-        <v>0.2025599521816953</v>
+        <v>0.1963812331802752</v>
       </c>
       <c r="I493" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>7.3</v>
       </c>
       <c r="H494" t="n">
-        <v>0.1507342064672044</v>
+        <v>0.1425547531785913</v>
       </c>
       <c r="I494" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>33.04</v>
       </c>
       <c r="H495" t="n">
-        <v>0.1284542599213371</v>
+        <v>0.118102505416357</v>
       </c>
       <c r="I495" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>38.82</v>
       </c>
       <c r="H496" t="n">
-        <v>0.204967465995731</v>
+        <v>0.1986881401364514</v>
       </c>
       <c r="I496" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>7.76</v>
       </c>
       <c r="H497" t="n">
-        <v>0.178794891497022</v>
+        <v>0.1814815603126664</v>
       </c>
       <c r="I497" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>11.9</v>
       </c>
       <c r="H498" t="n">
-        <v>0.1438349658220239</v>
+        <v>0.1368753474364815</v>
       </c>
       <c r="I498" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>1.5</v>
       </c>
       <c r="H499" t="n">
-        <v>0.04874516831655562</v>
+        <v>0.05906909555671602</v>
       </c>
       <c r="I499" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>13.15</v>
       </c>
       <c r="H500" t="n">
-        <v>0.1445461665221155</v>
+        <v>0.1473447821704174</v>
       </c>
       <c r="I500" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>8.15</v>
       </c>
       <c r="H501" t="n">
-        <v>0.1243998312560652</v>
+        <v>0.1231652778105835</v>
       </c>
       <c r="I501" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>7.45</v>
       </c>
       <c r="H502" t="n">
-        <v>0.1424309785231558</v>
+        <v>0.1440295416609054</v>
       </c>
       <c r="I502" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>150.98</v>
       </c>
       <c r="H503" t="n">
-        <v>-7.079425724121347e-05</v>
+        <v>-0.01113869681217783</v>
       </c>
       <c r="I503" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>5.8</v>
       </c>
       <c r="H504" t="n">
-        <v>0.1586018473249608</v>
+        <v>0.1583283940959832</v>
       </c>
       <c r="I504" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>11.59</v>
       </c>
       <c r="H505" t="n">
-        <v>0.02076044523697451</v>
+        <v>0.009472740843187832</v>
       </c>
       <c r="I505" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>23.69</v>
       </c>
       <c r="H506" t="n">
-        <v>0.1401543904507059</v>
+        <v>0.1334865055578808</v>
       </c>
       <c r="I506" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>65.09999999999999</v>
       </c>
       <c r="H507" t="n">
-        <v>0.1892844821733102</v>
+        <v>0.1788823718700734</v>
       </c>
       <c r="I507" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>1.31</v>
       </c>
       <c r="H508" t="n">
-        <v>0.0603891381492665</v>
+        <v>0.06645851326776275</v>
       </c>
       <c r="I508" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>59.66</v>
       </c>
       <c r="H509" t="n">
-        <v>0.1917339015995584</v>
+        <v>0.1816971502793647</v>
       </c>
       <c r="I509" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>21.03</v>
       </c>
       <c r="H510" t="n">
-        <v>0.09087618465932124</v>
+        <v>0.09427061465245634</v>
       </c>
       <c r="I510" t="inlineStr">
         <is>
@@ -16277,7 +16277,7 @@
         <v>28.36</v>
       </c>
       <c r="H511" t="n">
-        <v>-0.007896320848021166</v>
+        <v>-0.01841515125364734</v>
       </c>
       <c r="I511" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>6.64</v>
       </c>
       <c r="H512" t="n">
-        <v>0.1173765258786342</v>
+        <v>0.1200895975291659</v>
       </c>
       <c r="I512" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>12.18</v>
       </c>
       <c r="H513" t="n">
-        <v>0.09656348903793432</v>
+        <v>0.1017023005228378</v>
       </c>
       <c r="I513" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>10.24</v>
       </c>
       <c r="H514" t="n">
-        <v>0.06430096729719992</v>
+        <v>0.06727220172448733</v>
       </c>
       <c r="I514" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>21.22</v>
       </c>
       <c r="H515" t="n">
-        <v>0.1431409130729628</v>
+        <v>0.139131643017208</v>
       </c>
       <c r="I515" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>12.7</v>
       </c>
       <c r="H516" t="n">
-        <v>0.1205434831044041</v>
+        <v>0.1211669430123337</v>
       </c>
       <c r="I516" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>15.61</v>
       </c>
       <c r="H517" t="n">
-        <v>0.06604623334133186</v>
+        <v>0.07614562556903393</v>
       </c>
       <c r="I517" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>34.4</v>
       </c>
       <c r="H518" t="n">
-        <v>0.2171351828492891</v>
+        <v>0.2118186793584984</v>
       </c>
       <c r="I518" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>1.92</v>
       </c>
       <c r="H519" t="n">
-        <v>0.1191007542633088</v>
+        <v>0.1113263514843399</v>
       </c>
       <c r="I519" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>47.14</v>
       </c>
       <c r="H520" t="n">
-        <v>0.2124784125498899</v>
+        <v>0.1939406647622675</v>
       </c>
       <c r="I520" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>7.93</v>
       </c>
       <c r="H521" t="n">
-        <v>0.1239637371904453</v>
+        <v>0.1197215901759618</v>
       </c>
       <c r="I521" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>14.63</v>
       </c>
       <c r="H522" t="n">
-        <v>0.2221895883261621</v>
+        <v>0.2173872422575727</v>
       </c>
       <c r="I522" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>22.28</v>
       </c>
       <c r="H523" t="n">
-        <v>0.132569636651743</v>
+        <v>0.1200308610862165</v>
       </c>
       <c r="I523" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>31.44</v>
       </c>
       <c r="H524" t="n">
-        <v>0.2189663543567291</v>
+        <v>0.2123905422314257</v>
       </c>
       <c r="I524" t="inlineStr">
         <is>
@@ -16711,11 +16711,11 @@
         <v>169.27</v>
       </c>
       <c r="H525" t="n">
-        <v>0.008950313738043003</v>
+        <v>-0.001884683266516696</v>
       </c>
       <c r="I525" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Suspicious</t>
         </is>
       </c>
     </row>
@@ -16742,7 +16742,7 @@
         <v>19.59</v>
       </c>
       <c r="H526" t="n">
-        <v>0.1358538632334534</v>
+        <v>0.1386891177165905</v>
       </c>
       <c r="I526" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>62.69</v>
       </c>
       <c r="H527" t="n">
-        <v>0.1914058971816702</v>
+        <v>0.1838595541629475</v>
       </c>
       <c r="I527" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>34.49</v>
       </c>
       <c r="H528" t="n">
-        <v>0.1405783644317998</v>
+        <v>0.1329999605720655</v>
       </c>
       <c r="I528" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>4.3</v>
       </c>
       <c r="H529" t="n">
-        <v>0.06248979060152626</v>
+        <v>0.07549136460008177</v>
       </c>
       <c r="I529" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
         <v>11.52</v>
       </c>
       <c r="H530" t="n">
-        <v>0.07174359261671348</v>
+        <v>0.07213127942773601</v>
       </c>
       <c r="I530" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>22.98</v>
       </c>
       <c r="H531" t="n">
-        <v>0.1129307001760396</v>
+        <v>0.111303437205028</v>
       </c>
       <c r="I531" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>12.54</v>
       </c>
       <c r="H532" t="n">
-        <v>0.220559034116118</v>
+        <v>0.2137467922250724</v>
       </c>
       <c r="I532" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>38.73</v>
       </c>
       <c r="H533" t="n">
-        <v>0.0741234536855313</v>
+        <v>0.0758713100169659</v>
       </c>
       <c r="I533" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>11.26</v>
       </c>
       <c r="H534" t="n">
-        <v>0.1900110167534108</v>
+        <v>0.1900948408514333</v>
       </c>
       <c r="I534" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>17.62</v>
       </c>
       <c r="H535" t="n">
-        <v>0.225317017447544</v>
+        <v>0.2191304707282029</v>
       </c>
       <c r="I535" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>11.68</v>
       </c>
       <c r="H536" t="n">
-        <v>0.1916880637534526</v>
+        <v>0.1894571478023999</v>
       </c>
       <c r="I536" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>5.33</v>
       </c>
       <c r="H537" t="n">
-        <v>0.1308886343745858</v>
+        <v>0.1204255191206917</v>
       </c>
       <c r="I537" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>29.67</v>
       </c>
       <c r="H538" t="n">
-        <v>0.2241795488246049</v>
+        <v>0.2097852695536306</v>
       </c>
       <c r="I538" t="inlineStr">
         <is>
@@ -17145,7 +17145,7 @@
         <v>5.79</v>
       </c>
       <c r="H539" t="n">
-        <v>0.1996817200491444</v>
+        <v>0.1880397985177409</v>
       </c>
       <c r="I539" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>18.47</v>
       </c>
       <c r="H540" t="n">
-        <v>0.2386687018986355</v>
+        <v>0.2296205129382592</v>
       </c>
       <c r="I540" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>29.69</v>
       </c>
       <c r="H541" t="n">
-        <v>0.2201850324916077</v>
+        <v>0.2172033357960003</v>
       </c>
       <c r="I541" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>11.83</v>
       </c>
       <c r="H542" t="n">
-        <v>0.2223753834142781</v>
+        <v>0.2120142725660842</v>
       </c>
       <c r="I542" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>43.53</v>
       </c>
       <c r="H543" t="n">
-        <v>0.06751080566042789</v>
+        <v>0.07087822165383995</v>
       </c>
       <c r="I543" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>19.72</v>
       </c>
       <c r="H544" t="n">
-        <v>0.187280734948078</v>
+        <v>0.1895078220949353</v>
       </c>
       <c r="I544" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>69.64</v>
       </c>
       <c r="H545" t="n">
-        <v>0.1759395047270274</v>
+        <v>0.1628221808035378</v>
       </c>
       <c r="I545" t="inlineStr">
         <is>
@@ -17362,11 +17362,11 @@
         <v>61.78</v>
       </c>
       <c r="H546" t="n">
-        <v>-0.007447309852675832</v>
+        <v>0.008559060192859902</v>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>Suspicious</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -17393,7 +17393,7 @@
         <v>30.58</v>
       </c>
       <c r="H547" t="n">
-        <v>0.219495012728173</v>
+        <v>0.2147521387548311</v>
       </c>
       <c r="I547" t="inlineStr">
         <is>
@@ -17424,7 +17424,7 @@
         <v>16.78</v>
       </c>
       <c r="H548" t="n">
-        <v>0.1116832272340428</v>
+        <v>0.1024651277598615</v>
       </c>
       <c r="I548" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>16.02</v>
       </c>
       <c r="H549" t="n">
-        <v>0.2287483389340773</v>
+        <v>0.2162501661184313</v>
       </c>
       <c r="I549" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>22.85</v>
       </c>
       <c r="H550" t="n">
-        <v>0.2221558545013801</v>
+        <v>0.2158312586693104</v>
       </c>
       <c r="I550" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>34.08</v>
       </c>
       <c r="H551" t="n">
-        <v>0.2205629426899813</v>
+        <v>0.2086629624016738</v>
       </c>
       <c r="I551" t="inlineStr">
         <is>
@@ -17548,7 +17548,7 @@
         <v>18.09</v>
       </c>
       <c r="H552" t="n">
-        <v>-0.04448108883336044</v>
+        <v>-0.04741049715580836</v>
       </c>
       <c r="I552" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>20.27</v>
       </c>
       <c r="H553" t="n">
-        <v>0.2286601587860084</v>
+        <v>0.2174697297316865</v>
       </c>
       <c r="I553" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>19.85</v>
       </c>
       <c r="H554" t="n">
-        <v>0.1463510054290705</v>
+        <v>0.1429448048699965</v>
       </c>
       <c r="I554" t="inlineStr">
         <is>
@@ -17641,7 +17641,7 @@
         <v>6.88</v>
       </c>
       <c r="H555" t="n">
-        <v>0.1430756711700789</v>
+        <v>0.1354043333448546</v>
       </c>
       <c r="I555" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>39.51</v>
       </c>
       <c r="H556" t="n">
-        <v>0.1341324327963482</v>
+        <v>0.125188414762615</v>
       </c>
       <c r="I556" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>32.34</v>
       </c>
       <c r="H557" t="n">
-        <v>0.06800854640949916</v>
+        <v>0.06448861356852542</v>
       </c>
       <c r="I557" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>41.73</v>
       </c>
       <c r="H558" t="n">
-        <v>0.2121175780272766</v>
+        <v>0.2060409292706775</v>
       </c>
       <c r="I558" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>11.7</v>
       </c>
       <c r="H559" t="n">
-        <v>0.2117806217076842</v>
+        <v>0.2057847184250021</v>
       </c>
       <c r="I559" t="inlineStr">
         <is>
@@ -17796,7 +17796,7 @@
         <v>1.63</v>
       </c>
       <c r="H560" t="n">
-        <v>-0.01271470015051435</v>
+        <v>-0.01504407050268775</v>
       </c>
       <c r="I560" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>17.9</v>
       </c>
       <c r="H561" t="n">
-        <v>-0.03896103147395713</v>
+        <v>-0.03581141437885094</v>
       </c>
       <c r="I561" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>30.86</v>
       </c>
       <c r="H562" t="n">
-        <v>0.09498197971200817</v>
+        <v>0.0918738069067685</v>
       </c>
       <c r="I562" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>27.9</v>
       </c>
       <c r="H563" t="n">
-        <v>0.1024842785153717</v>
+        <v>0.1012690376653188</v>
       </c>
       <c r="I563" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>40.59</v>
       </c>
       <c r="H564" t="n">
-        <v>0.07398138951226418</v>
+        <v>0.07069763911310378</v>
       </c>
       <c r="I564" t="inlineStr">
         <is>
@@ -17951,7 +17951,7 @@
         <v>22.25</v>
       </c>
       <c r="H565" t="n">
-        <v>0.2379066615832995</v>
+        <v>0.2310384952270403</v>
       </c>
       <c r="I565" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>24.78</v>
       </c>
       <c r="H566" t="n">
-        <v>0.0603854800804593</v>
+        <v>0.05039215498002381</v>
       </c>
       <c r="I566" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>52.6</v>
       </c>
       <c r="H567" t="n">
-        <v>0.1997271196146881</v>
+        <v>0.1872511686855126</v>
       </c>
       <c r="I567" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>17.77</v>
       </c>
       <c r="H568" t="n">
-        <v>0.2398396133628335</v>
+        <v>0.2294116078285395</v>
       </c>
       <c r="I568" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>32.25</v>
       </c>
       <c r="H569" t="n">
-        <v>0.229774917740731</v>
+        <v>0.2251437985042919</v>
       </c>
       <c r="I569" t="inlineStr">
         <is>
@@ -18106,7 +18106,7 @@
         <v>39.88</v>
       </c>
       <c r="H570" t="n">
-        <v>0.08175545308681709</v>
+        <v>0.08321500945440674</v>
       </c>
       <c r="I570" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>6.98</v>
       </c>
       <c r="H571" t="n">
-        <v>0.0754882391479913</v>
+        <v>0.08437887918974274</v>
       </c>
       <c r="I571" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>16.29</v>
       </c>
       <c r="H572" t="n">
-        <v>0.1452363011925794</v>
+        <v>0.1402694732141164</v>
       </c>
       <c r="I572" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>25.6</v>
       </c>
       <c r="H573" t="n">
-        <v>0.1189660778463419</v>
+        <v>0.1243403714893413</v>
       </c>
       <c r="I573" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>19.04</v>
       </c>
       <c r="H574" t="n">
-        <v>0.1659855299685131</v>
+        <v>0.1643150464114924</v>
       </c>
       <c r="I574" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>11.12</v>
       </c>
       <c r="H575" t="n">
-        <v>0.05972457829635358</v>
+        <v>0.06809641515945475</v>
       </c>
       <c r="I575" t="inlineStr">
         <is>
@@ -18292,7 +18292,7 @@
         <v>15.53</v>
       </c>
       <c r="H576" t="n">
-        <v>0.1513324018689767</v>
+        <v>0.1449073446180751</v>
       </c>
       <c r="I576" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>51.34</v>
       </c>
       <c r="H577" t="n">
-        <v>0.1730620975297882</v>
+        <v>0.1591423807961976</v>
       </c>
       <c r="I577" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>5.06</v>
       </c>
       <c r="H578" t="n">
-        <v>0.1243181655843126</v>
+        <v>0.1221034968820911</v>
       </c>
       <c r="I578" t="inlineStr">
         <is>
@@ -18385,7 +18385,7 @@
         <v>15.34</v>
       </c>
       <c r="H579" t="n">
-        <v>0.2233394962375828</v>
+        <v>0.2184262921173055</v>
       </c>
       <c r="I579" t="inlineStr">
         <is>
@@ -18416,7 +18416,7 @@
         <v>5.73</v>
       </c>
       <c r="H580" t="n">
-        <v>0.02963637431427102</v>
+        <v>0.01996859510702309</v>
       </c>
       <c r="I580" t="inlineStr">
         <is>
@@ -18447,7 +18447,7 @@
         <v>17.3</v>
       </c>
       <c r="H581" t="n">
-        <v>0.2387190093505357</v>
+        <v>0.2292087372609749</v>
       </c>
       <c r="I581" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>25.64</v>
       </c>
       <c r="H582" t="n">
-        <v>0.05581323988622766</v>
+        <v>0.04447456881618428</v>
       </c>
       <c r="I582" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>2.28</v>
       </c>
       <c r="H583" t="n">
-        <v>0.06432868222700272</v>
+        <v>0.06920303109036219</v>
       </c>
       <c r="I583" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>10.87</v>
       </c>
       <c r="H584" t="n">
-        <v>0.2092040374806666</v>
+        <v>0.2042552013132919</v>
       </c>
       <c r="I584" t="inlineStr">
         <is>
@@ -18571,7 +18571,7 @@
         <v>19.02</v>
       </c>
       <c r="H585" t="n">
-        <v>0.1605883324482807</v>
+        <v>0.1708063535365713</v>
       </c>
       <c r="I585" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>20.48</v>
       </c>
       <c r="H586" t="n">
-        <v>0.1375581173615126</v>
+        <v>0.1384375001694629</v>
       </c>
       <c r="I586" t="inlineStr">
         <is>
@@ -18633,7 +18633,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="H587" t="n">
-        <v>-0.001965445490415663</v>
+        <v>-0.01848014309650037</v>
       </c>
       <c r="I587" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>35.5</v>
       </c>
       <c r="H588" t="n">
-        <v>0.227169793291997</v>
+        <v>0.2217336982508584</v>
       </c>
       <c r="I588" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>19.62</v>
       </c>
       <c r="H589" t="n">
-        <v>0.2279286678259131</v>
+        <v>0.2236493747510139</v>
       </c>
       <c r="I589" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>157.09</v>
       </c>
       <c r="H590" t="n">
-        <v>0.02700429065539478</v>
+        <v>0.03930086334127481</v>
       </c>
       <c r="I590" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>25.79</v>
       </c>
       <c r="H591" t="n">
-        <v>0.2380141468315599</v>
+        <v>0.2282822349148109</v>
       </c>
       <c r="I591" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>10.97</v>
       </c>
       <c r="H592" t="n">
-        <v>0.1658695011923929</v>
+        <v>0.1665513228964267</v>
       </c>
       <c r="I592" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>17.69</v>
       </c>
       <c r="H593" t="n">
-        <v>0.151371134043899</v>
+        <v>0.1469542410347258</v>
       </c>
       <c r="I593" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>14.71</v>
       </c>
       <c r="H594" t="n">
-        <v>0.2363120850359483</v>
+        <v>0.2273906464231457</v>
       </c>
       <c r="I594" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
         <v>28.59</v>
       </c>
       <c r="H595" t="n">
-        <v>0.2343003907387635</v>
+        <v>0.2262950468697726</v>
       </c>
       <c r="I595" t="inlineStr">
         <is>
@@ -18912,7 +18912,7 @@
         <v>3.88</v>
       </c>
       <c r="H596" t="n">
-        <v>0.1276830479670257</v>
+        <v>0.126118712609439</v>
       </c>
       <c r="I596" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>18.9</v>
       </c>
       <c r="H597" t="n">
-        <v>0.2197221792734939</v>
+        <v>0.2124024740807752</v>
       </c>
       <c r="I597" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>19.36</v>
       </c>
       <c r="H598" t="n">
-        <v>0.2281219396046955</v>
+        <v>0.2179109724708245</v>
       </c>
       <c r="I598" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>39.91</v>
       </c>
       <c r="H599" t="n">
-        <v>0.2135244607771848</v>
+        <v>0.2078448234580845</v>
       </c>
       <c r="I599" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>37.17</v>
       </c>
       <c r="H600" t="n">
-        <v>0.2253884398065754</v>
+        <v>0.2189912228518912</v>
       </c>
       <c r="I600" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>11.63</v>
       </c>
       <c r="H601" t="n">
-        <v>0.1322349551765153</v>
+        <v>0.1279574054585239</v>
       </c>
       <c r="I601" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>38.8</v>
       </c>
       <c r="H602" t="n">
-        <v>0.2142926261804622</v>
+        <v>0.2078791462811632</v>
       </c>
       <c r="I602" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>21.38</v>
       </c>
       <c r="H603" t="n">
-        <v>0.2383563808891723</v>
+        <v>0.2310515479004766</v>
       </c>
       <c r="I603" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>21.65</v>
       </c>
       <c r="H604" t="n">
-        <v>0.2387958088217175</v>
+        <v>0.2301165123187745</v>
       </c>
       <c r="I604" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>15.37</v>
       </c>
       <c r="H605" t="n">
-        <v>0.2285643320867078</v>
+        <v>0.2221454888527744</v>
       </c>
       <c r="I605" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>67.90000000000001</v>
       </c>
       <c r="H606" t="n">
-        <v>0.187254143770249</v>
+        <v>0.1776108622562947</v>
       </c>
       <c r="I606" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>63.05</v>
       </c>
       <c r="H607" t="n">
-        <v>0.184926735089562</v>
+        <v>0.1711147969426532</v>
       </c>
       <c r="I607" t="inlineStr">
         <is>
@@ -19284,7 +19284,7 @@
         <v>9.02</v>
       </c>
       <c r="H608" t="n">
-        <v>0.1590680232599663</v>
+        <v>0.1725865272963962</v>
       </c>
       <c r="I608" t="inlineStr">
         <is>
@@ -19315,7 +19315,7 @@
         <v>11.06</v>
       </c>
       <c r="H609" t="n">
-        <v>0.088616988752243</v>
+        <v>0.08434210374925277</v>
       </c>
       <c r="I609" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>21.64</v>
       </c>
       <c r="H610" t="n">
-        <v>0.007154839604763041</v>
+        <v>0.004385733930312163</v>
       </c>
       <c r="I610" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>24.72</v>
       </c>
       <c r="H611" t="n">
-        <v>0.1293836467205322</v>
+        <v>0.1204079752333579</v>
       </c>
       <c r="I611" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>172.62</v>
       </c>
       <c r="H612" t="n">
-        <v>-0.04749694415889272</v>
+        <v>-0.04122062698801399</v>
       </c>
       <c r="I612" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>10.2</v>
       </c>
       <c r="H613" t="n">
-        <v>0.1870388160586636</v>
+        <v>0.1896690763261327</v>
       </c>
       <c r="I613" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>34.69</v>
       </c>
       <c r="H614" t="n">
-        <v>0.2193937044519028</v>
+        <v>0.2087210679282607</v>
       </c>
       <c r="I614" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>5.18</v>
       </c>
       <c r="H615" t="n">
-        <v>0.2169146536115367</v>
+        <v>0.2122682190383783</v>
       </c>
       <c r="I615" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>12.72</v>
       </c>
       <c r="H616" t="n">
-        <v>0.1943528701900066</v>
+        <v>0.190897504495694</v>
       </c>
       <c r="I616" t="inlineStr">
         <is>
@@ -19563,7 +19563,7 @@
         <v>43.16</v>
       </c>
       <c r="H617" t="n">
-        <v>0.2100221995832451</v>
+        <v>0.2027964320743448</v>
       </c>
       <c r="I617" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>26.83</v>
       </c>
       <c r="H618" t="n">
-        <v>0.1226174867881372</v>
+        <v>0.1122389204815063</v>
       </c>
       <c r="I618" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>46.68</v>
       </c>
       <c r="H619" t="n">
-        <v>0.1160443082798386</v>
+        <v>0.111206901067334</v>
       </c>
       <c r="I619" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>66.29000000000001</v>
       </c>
       <c r="H620" t="n">
-        <v>0.04439855018423811</v>
+        <v>0.03969652723440675</v>
       </c>
       <c r="I620" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>22.87</v>
       </c>
       <c r="H621" t="n">
-        <v>0.05822433410843431</v>
+        <v>0.06666442342534229</v>
       </c>
       <c r="I621" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>16.77</v>
       </c>
       <c r="H622" t="n">
-        <v>0.2390672351002187</v>
+        <v>0.2280114244748928</v>
       </c>
       <c r="I622" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>7.24</v>
       </c>
       <c r="H623" t="n">
-        <v>0.1138605582416657</v>
+        <v>0.1060357798167996</v>
       </c>
       <c r="I623" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>31.19</v>
       </c>
       <c r="H624" t="n">
-        <v>0.2303313234531297</v>
+        <v>0.2248321303043793</v>
       </c>
       <c r="I624" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>2.73</v>
       </c>
       <c r="H625" t="n">
-        <v>-0.002893166519839285</v>
+        <v>-0.01257001266096691</v>
       </c>
       <c r="I625" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>18.61</v>
       </c>
       <c r="H626" t="n">
-        <v>0.06518390777348926</v>
+        <v>0.05283467522656693</v>
       </c>
       <c r="I626" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>13.71</v>
       </c>
       <c r="H627" t="n">
-        <v>0.08355542967156038</v>
+        <v>0.08188748236651799</v>
       </c>
       <c r="I627" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>32.99</v>
       </c>
       <c r="H628" t="n">
-        <v>0.2085357231380229</v>
+        <v>0.2057808694621019</v>
       </c>
       <c r="I628" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>25.5</v>
       </c>
       <c r="H629" t="n">
-        <v>0.1297390407052126</v>
+        <v>0.1180710672313233</v>
       </c>
       <c r="I629" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>154.72</v>
       </c>
       <c r="H630" t="n">
-        <v>0.03399392382495448</v>
+        <v>0.04324773355128153</v>
       </c>
       <c r="I630" t="inlineStr">
         <is>
@@ -19997,7 +19997,7 @@
         <v>6.9</v>
       </c>
       <c r="H631" t="n">
-        <v>0.2166773356652966</v>
+        <v>0.2110967348412442</v>
       </c>
       <c r="I631" t="inlineStr">
         <is>
@@ -20028,7 +20028,7 @@
         <v>5.5</v>
       </c>
       <c r="H632" t="n">
-        <v>0.1291607982983587</v>
+        <v>0.127580336348789</v>
       </c>
       <c r="I632" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>2.33</v>
       </c>
       <c r="H633" t="n">
-        <v>0.1855539121555959</v>
+        <v>0.1846750543316072</v>
       </c>
       <c r="I633" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
         <v>13.95</v>
       </c>
       <c r="H634" t="n">
-        <v>0.1449417600426358</v>
+        <v>0.1410599262158624</v>
       </c>
       <c r="I634" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>1.02</v>
       </c>
       <c r="H635" t="n">
-        <v>0.1166299769320364</v>
+        <v>0.1140973848286539</v>
       </c>
       <c r="I635" t="inlineStr">
         <is>
@@ -20152,7 +20152,7 @@
         <v>2.65</v>
       </c>
       <c r="H636" t="n">
-        <v>0.09679952252278679</v>
+        <v>0.09261253889673571</v>
       </c>
       <c r="I636" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>30.95</v>
       </c>
       <c r="H637" t="n">
-        <v>0.05295951043257052</v>
+        <v>0.03334551821661946</v>
       </c>
       <c r="I637" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>5.81</v>
       </c>
       <c r="H638" t="n">
-        <v>0.07782496590226173</v>
+        <v>0.07980221919451125</v>
       </c>
       <c r="I638" t="inlineStr">
         <is>
@@ -20245,7 +20245,7 @@
         <v>24.47</v>
       </c>
       <c r="H639" t="n">
-        <v>0.2387038936066696</v>
+        <v>0.2289138917311257</v>
       </c>
       <c r="I639" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>3.21</v>
       </c>
       <c r="H640" t="n">
-        <v>0.1258194891007127</v>
+        <v>0.1190443776199517</v>
       </c>
       <c r="I640" t="inlineStr">
         <is>
@@ -20307,7 +20307,7 @@
         <v>5.31</v>
       </c>
       <c r="H641" t="n">
-        <v>0.1218765118232479</v>
+        <v>0.1122920584109368</v>
       </c>
       <c r="I641" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>35.19</v>
       </c>
       <c r="H642" t="n">
-        <v>0.04386624707029785</v>
+        <v>0.02666712176590147</v>
       </c>
       <c r="I642" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>6.08</v>
       </c>
       <c r="H643" t="n">
-        <v>0.07424413154478193</v>
+        <v>0.06917622706204729</v>
       </c>
       <c r="I643" t="inlineStr">
         <is>
@@ -20400,7 +20400,7 @@
         <v>22.86</v>
       </c>
       <c r="H644" t="n">
-        <v>0.2386938109245562</v>
+        <v>0.2294271903789553</v>
       </c>
       <c r="I644" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>18.02</v>
       </c>
       <c r="H645" t="n">
-        <v>0.187892799710454</v>
+        <v>0.1915175308199194</v>
       </c>
       <c r="I645" t="inlineStr">
         <is>
@@ -20462,7 +20462,7 @@
         <v>15.24</v>
       </c>
       <c r="H646" t="n">
-        <v>0.2178877432328652</v>
+        <v>0.2117618115844396</v>
       </c>
       <c r="I646" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>2.17</v>
       </c>
       <c r="H647" t="n">
-        <v>0.1265478970463995</v>
+        <v>0.1247784295888137</v>
       </c>
       <c r="I647" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>17.58</v>
       </c>
       <c r="H648" t="n">
-        <v>0.1375650561861443</v>
+        <v>0.1396199456723817</v>
       </c>
       <c r="I648" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>10.26</v>
       </c>
       <c r="H649" t="n">
-        <v>0.1136993454206006</v>
+        <v>0.1120235616906666</v>
       </c>
       <c r="I649" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>9.42</v>
       </c>
       <c r="H650" t="n">
-        <v>0.117739588331652</v>
+        <v>0.1174903635023177</v>
       </c>
       <c r="I650" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>4.56</v>
       </c>
       <c r="H651" t="n">
-        <v>0.1184938583023125</v>
+        <v>0.1322140772502152</v>
       </c>
       <c r="I651" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>56.74</v>
       </c>
       <c r="H652" t="n">
-        <v>0.1973858047576135</v>
+        <v>0.1870288034403519</v>
       </c>
       <c r="I652" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>9.65</v>
       </c>
       <c r="H653" t="n">
-        <v>0.2117743592477073</v>
+        <v>0.2086053317540081</v>
       </c>
       <c r="I653" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>18.28</v>
       </c>
       <c r="H654" t="n">
-        <v>0.1382492892116399</v>
+        <v>0.1287961036859068</v>
       </c>
       <c r="I654" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>29.25</v>
       </c>
       <c r="H655" t="n">
-        <v>0.2214904377152139</v>
+        <v>0.212462683604127</v>
       </c>
       <c r="I655" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>4.72</v>
       </c>
       <c r="H656" t="n">
-        <v>0.2078717848347386</v>
+        <v>0.2045598079722966</v>
       </c>
       <c r="I656" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>75.62</v>
       </c>
       <c r="H657" t="n">
-        <v>0.05087140494697462</v>
+        <v>0.04829428620910925</v>
       </c>
       <c r="I657" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>59.23</v>
       </c>
       <c r="H658" t="n">
-        <v>0.1766928434310994</v>
+        <v>0.1695134380785259</v>
       </c>
       <c r="I658" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>0.72</v>
       </c>
       <c r="H659" t="n">
-        <v>0.1030388234745104</v>
+        <v>0.1070421134057571</v>
       </c>
       <c r="I659" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>105.45</v>
       </c>
       <c r="H660" t="n">
-        <v>0.07847058381014405</v>
+        <v>0.06963191808339442</v>
       </c>
       <c r="I660" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>1.56</v>
       </c>
       <c r="H661" t="n">
-        <v>0.1180252542076987</v>
+        <v>0.1122625403732778</v>
       </c>
       <c r="I661" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>28.68</v>
       </c>
       <c r="H662" t="n">
-        <v>0.2227367256994108</v>
+        <v>0.2180589507705791</v>
       </c>
       <c r="I662" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>2.67</v>
       </c>
       <c r="H663" t="n">
-        <v>0.1165043618523941</v>
+        <v>0.1071004706399229</v>
       </c>
       <c r="I663" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>5.76</v>
       </c>
       <c r="H664" t="n">
-        <v>0.09366574530693428</v>
+        <v>0.08244041758494869</v>
       </c>
       <c r="I664" t="inlineStr">
         <is>
@@ -21051,7 +21051,7 @@
         <v>51.12</v>
       </c>
       <c r="H665" t="n">
-        <v>0.1862145838193157</v>
+        <v>0.180342212098019</v>
       </c>
       <c r="I665" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>7.43</v>
       </c>
       <c r="H666" t="n">
-        <v>0.1183466963641198</v>
+        <v>0.1124121560367147</v>
       </c>
       <c r="I666" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>29.98</v>
       </c>
       <c r="H667" t="n">
-        <v>0.05111648894091636</v>
+        <v>0.03918669573116873</v>
       </c>
       <c r="I667" t="inlineStr">
         <is>
@@ -21144,7 +21144,7 @@
         <v>12.92</v>
       </c>
       <c r="H668" t="n">
-        <v>0.1582544580858987</v>
+        <v>0.1526690566358336</v>
       </c>
       <c r="I668" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>10.52</v>
       </c>
       <c r="H669" t="n">
-        <v>0.09517195048746174</v>
+        <v>0.09225519477313071</v>
       </c>
       <c r="I669" t="inlineStr">
         <is>
@@ -21206,7 +21206,7 @@
         <v>89.62</v>
       </c>
       <c r="H670" t="n">
-        <v>0.1370344225372362</v>
+        <v>0.1315132073413104</v>
       </c>
       <c r="I670" t="inlineStr">
         <is>
@@ -21237,7 +21237,7 @@
         <v>15.8</v>
       </c>
       <c r="H671" t="n">
-        <v>0.111854368148117</v>
+        <v>0.1039031803935503</v>
       </c>
       <c r="I671" t="inlineStr">
         <is>
@@ -21268,7 +21268,7 @@
         <v>16.37</v>
       </c>
       <c r="H672" t="n">
-        <v>0.2394126212006814</v>
+        <v>0.2276160842512555</v>
       </c>
       <c r="I672" t="inlineStr">
         <is>
@@ -21299,7 +21299,7 @@
         <v>1.97</v>
       </c>
       <c r="H673" t="n">
-        <v>0.12548681514912</v>
+        <v>0.1238648437739903</v>
       </c>
       <c r="I673" t="inlineStr">
         <is>
@@ -21330,7 +21330,7 @@
         <v>7.08</v>
       </c>
       <c r="H674" t="n">
-        <v>0.1108389086685706</v>
+        <v>0.1033956758957835</v>
       </c>
       <c r="I674" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>8.619999999999999</v>
       </c>
       <c r="H675" t="n">
-        <v>0.1122836752091524</v>
+        <v>0.1106806653109795</v>
       </c>
       <c r="I675" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>2.92</v>
       </c>
       <c r="H676" t="n">
-        <v>0.09871370359576337</v>
+        <v>0.09528563677391599</v>
       </c>
       <c r="I676" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>68.08</v>
       </c>
       <c r="H677" t="n">
-        <v>0.168456365647292</v>
+        <v>0.1623352632411844</v>
       </c>
       <c r="I677" t="inlineStr">
         <is>
@@ -21454,7 +21454,7 @@
         <v>37.24</v>
       </c>
       <c r="H678" t="n">
-        <v>0.2249607287066497</v>
+        <v>0.2202411726024453</v>
       </c>
       <c r="I678" t="inlineStr">
         <is>
@@ -21485,7 +21485,7 @@
         <v>24.35</v>
       </c>
       <c r="H679" t="n">
-        <v>0.05554420213165001</v>
+        <v>0.04526887900464649</v>
       </c>
       <c r="I679" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>21.01</v>
       </c>
       <c r="H680" t="n">
-        <v>0.1431409130729628</v>
+        <v>0.139298304917081</v>
       </c>
       <c r="I680" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>8.81</v>
       </c>
       <c r="H681" t="n">
-        <v>0.2091088404705936</v>
+        <v>0.2064392733599191</v>
       </c>
       <c r="I681" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>39.33</v>
       </c>
       <c r="H682" t="n">
-        <v>0.2141891791578732</v>
+        <v>0.2074080304528897</v>
       </c>
       <c r="I682" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>1.68</v>
       </c>
       <c r="H683" t="n">
-        <v>0.09934795409234232</v>
+        <v>0.09415058380682773</v>
       </c>
       <c r="I683" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>14.57</v>
       </c>
       <c r="H684" t="n">
-        <v>0.04599924925262988</v>
+        <v>0.0422738674758546</v>
       </c>
       <c r="I684" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>3.83</v>
       </c>
       <c r="H685" t="n">
-        <v>0.1248261571838</v>
+        <v>0.1171984107151588</v>
       </c>
       <c r="I685" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>80.12</v>
       </c>
       <c r="H686" t="n">
-        <v>0.1477012020052371</v>
+        <v>0.1379370677140476</v>
       </c>
       <c r="I686" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>4.93</v>
       </c>
       <c r="H687" t="n">
-        <v>0.1245018392131253</v>
+        <v>0.1194676778189849</v>
       </c>
       <c r="I687" t="inlineStr">
         <is>
@@ -21764,11 +21764,11 @@
         <v>69.75</v>
       </c>
       <c r="H688" t="n">
-        <v>-0.01126871967907184</v>
+        <v>0.0003663023132188803</v>
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>Suspicious</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -21795,7 +21795,7 @@
         <v>29.5</v>
       </c>
       <c r="H689" t="n">
-        <v>0.210606416793149</v>
+        <v>0.2076264123033882</v>
       </c>
       <c r="I689" t="inlineStr">
         <is>
@@ -21826,7 +21826,7 @@
         <v>35.59</v>
       </c>
       <c r="H690" t="n">
-        <v>0.221286578361702</v>
+        <v>0.2110699782990539</v>
       </c>
       <c r="I690" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>54.02</v>
       </c>
       <c r="H691" t="n">
-        <v>0.01602862537041794</v>
+        <v>0.002214183010149862</v>
       </c>
       <c r="I691" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>15.97</v>
       </c>
       <c r="H692" t="n">
-        <v>0.1352273655993847</v>
+        <v>0.1423680804401059</v>
       </c>
       <c r="I692" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>11.91</v>
       </c>
       <c r="H693" t="n">
-        <v>0.232189888185628</v>
+        <v>0.2264267230844424</v>
       </c>
       <c r="I693" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>94.90000000000001</v>
       </c>
       <c r="H694" t="n">
-        <v>0.1357562058711541</v>
+        <v>0.1150306794412567</v>
       </c>
       <c r="I694" t="inlineStr">
         <is>
@@ -21981,7 +21981,7 @@
         <v>29.55</v>
       </c>
       <c r="H695" t="n">
-        <v>0.2323507450619</v>
+        <v>0.2266368071946459</v>
       </c>
       <c r="I695" t="inlineStr">
         <is>
@@ -22012,7 +22012,7 @@
         <v>5.58</v>
       </c>
       <c r="H696" t="n">
-        <v>0.08148119388672515</v>
+        <v>0.07722418436125977</v>
       </c>
       <c r="I696" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>22.2</v>
       </c>
       <c r="H697" t="n">
-        <v>0.2268497650698877</v>
+        <v>0.2194914617741742</v>
       </c>
       <c r="I697" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>10.42</v>
       </c>
       <c r="H698" t="n">
-        <v>0.159689613859768</v>
+        <v>0.1747842500672098</v>
       </c>
       <c r="I698" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>56.35</v>
       </c>
       <c r="H699" t="n">
-        <v>0.1927060631084874</v>
+        <v>0.178288933286937</v>
       </c>
       <c r="I699" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>16.41</v>
       </c>
       <c r="H700" t="n">
-        <v>0.01120709352687621</v>
+        <v>0.005267391609379168</v>
       </c>
       <c r="I700" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>17.41</v>
       </c>
       <c r="H701" t="n">
-        <v>0.05211002580460711</v>
+        <v>0.04428269539859719</v>
       </c>
       <c r="I701" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>8.619999999999999</v>
       </c>
       <c r="H702" t="n">
-        <v>0.1122836752091524</v>
+        <v>0.1106806653109795</v>
       </c>
       <c r="I702" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>11.11</v>
       </c>
       <c r="H703" t="n">
-        <v>0.1159793115929932</v>
+        <v>0.109728504905291</v>
       </c>
       <c r="I703" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>21.78</v>
       </c>
       <c r="H704" t="n">
-        <v>0.2262991168787911</v>
+        <v>0.2238773666805538</v>
       </c>
       <c r="I704" t="inlineStr">
         <is>
@@ -22291,7 +22291,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="H705" t="n">
-        <v>0.163868206218323</v>
+        <v>0.1625834138673877</v>
       </c>
       <c r="I705" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>8.23</v>
       </c>
       <c r="H706" t="n">
-        <v>0.1586933488884652</v>
+        <v>0.1717568268184061</v>
       </c>
       <c r="I706" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>62.5</v>
       </c>
       <c r="H707" t="n">
-        <v>0.04718139666432353</v>
+        <v>0.04199655450437612</v>
       </c>
       <c r="I707" t="inlineStr">
         <is>
@@ -22384,7 +22384,7 @@
         <v>46.64</v>
       </c>
       <c r="H708" t="n">
-        <v>0.2192271471420945</v>
+        <v>0.2125050653395251</v>
       </c>
       <c r="I708" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>2.87</v>
       </c>
       <c r="H709" t="n">
-        <v>0.1143590981702599</v>
+        <v>0.1127843670515891</v>
       </c>
       <c r="I709" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>9.18</v>
       </c>
       <c r="H710" t="n">
-        <v>0.2266003774191208</v>
+        <v>0.2229120975354385</v>
       </c>
       <c r="I710" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>5.25</v>
       </c>
       <c r="H711" t="n">
-        <v>0.1398712890949544</v>
+        <v>0.134274454669188</v>
       </c>
       <c r="I711" t="inlineStr">
         <is>
@@ -22508,7 +22508,7 @@
         <v>12.84</v>
       </c>
       <c r="H712" t="n">
-        <v>0.1443948401367118</v>
+        <v>0.1474286767003583</v>
       </c>
       <c r="I712" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>15.86</v>
       </c>
       <c r="H713" t="n">
-        <v>0.222859553876181</v>
+        <v>0.2157781931193081</v>
       </c>
       <c r="I713" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>41.41</v>
       </c>
       <c r="H714" t="n">
-        <v>0.09538407995277087</v>
+        <v>0.08427406163350137</v>
       </c>
       <c r="I714" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>17.2</v>
       </c>
       <c r="H715" t="n">
-        <v>0.2199076671976001</v>
+        <v>0.2124444815455829</v>
       </c>
       <c r="I715" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>60.27</v>
       </c>
       <c r="H716" t="n">
-        <v>0.05404299153712333</v>
+        <v>0.05284051781246901</v>
       </c>
       <c r="I716" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>3.8</v>
       </c>
       <c r="H717" t="n">
-        <v>0.1273398032008796</v>
+        <v>0.1264354174322341</v>
       </c>
       <c r="I717" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>97.06999999999999</v>
       </c>
       <c r="H718" t="n">
-        <v>0.1223702836418213</v>
+        <v>0.1085772202727873</v>
       </c>
       <c r="I718" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>10.29</v>
       </c>
       <c r="H719" t="n">
-        <v>-0.008959687373687686</v>
+        <v>-0.003791046919425334</v>
       </c>
       <c r="I719" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>3.49</v>
       </c>
       <c r="H720" t="n">
-        <v>0.09961975940814227</v>
+        <v>0.09531406059733349</v>
       </c>
       <c r="I720" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>45.89</v>
       </c>
       <c r="H721" t="n">
-        <v>0.03890737401813948</v>
+        <v>0.02816333491262357</v>
       </c>
       <c r="I721" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>22.04</v>
       </c>
       <c r="H722" t="n">
-        <v>0.1174275736123636</v>
+        <v>0.112116244564904</v>
       </c>
       <c r="I722" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>4.35</v>
       </c>
       <c r="H723" t="n">
-        <v>0.1461353625455292</v>
+        <v>0.1641074996403016</v>
       </c>
       <c r="I723" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>17.45</v>
       </c>
       <c r="H724" t="n">
-        <v>0.1549159570731654</v>
+        <v>0.1500117839559295</v>
       </c>
       <c r="I724" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>15.73</v>
       </c>
       <c r="H725" t="n">
-        <v>0.1968065597160725</v>
+        <v>0.1922642258232651</v>
       </c>
       <c r="I725" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>14.78</v>
       </c>
       <c r="H726" t="n">
-        <v>0.2225093640784061</v>
+        <v>0.2174747927137915</v>
       </c>
       <c r="I726" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>17.38</v>
       </c>
       <c r="H727" t="n">
-        <v>0.1461226059154446</v>
+        <v>0.1445338368573599</v>
       </c>
       <c r="I727" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>17.81</v>
       </c>
       <c r="H728" t="n">
-        <v>0.2192599550156943</v>
+        <v>0.2124187967002312</v>
       </c>
       <c r="I728" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>4.72</v>
       </c>
       <c r="H729" t="n">
-        <v>0.1259411485003417</v>
+        <v>0.124754648550176</v>
       </c>
       <c r="I729" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>5.64</v>
       </c>
       <c r="H730" t="n">
-        <v>0.08123308296738785</v>
+        <v>0.07508669210266805</v>
       </c>
       <c r="I730" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>4.6</v>
       </c>
       <c r="H731" t="n">
-        <v>0.2151057008388281</v>
+        <v>0.2097943487267601</v>
       </c>
       <c r="I731" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>47.18</v>
       </c>
       <c r="H732" t="n">
-        <v>0.2177976210715998</v>
+        <v>0.2111631309967349</v>
       </c>
       <c r="I732" t="inlineStr">
         <is>
@@ -23159,7 +23159,7 @@
         <v>37.52</v>
       </c>
       <c r="H733" t="n">
-        <v>0.1045219912189839</v>
+        <v>0.0903168400334643</v>
       </c>
       <c r="I733" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45.07</v>
       </c>
       <c r="H734" t="n">
-        <v>0.2136078544064968</v>
+        <v>0.1988788468671494</v>
       </c>
       <c r="I734" t="inlineStr">
         <is>
@@ -23221,7 +23221,7 @@
         <v>12.57</v>
       </c>
       <c r="H735" t="n">
-        <v>-0.01015327000548194</v>
+        <v>-0.005050632496207408</v>
       </c>
       <c r="I735" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>8.92</v>
       </c>
       <c r="H736" t="n">
-        <v>0.1282965746156415</v>
+        <v>0.1290204650336175</v>
       </c>
       <c r="I736" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>8.380000000000001</v>
       </c>
       <c r="H737" t="n">
-        <v>0.1131325849326089</v>
+        <v>0.1129007152518924</v>
       </c>
       <c r="I737" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>5.83</v>
       </c>
       <c r="H738" t="n">
-        <v>0.1163861772815813</v>
+        <v>0.1194927790702135</v>
       </c>
       <c r="I738" t="inlineStr">
         <is>
@@ -23345,7 +23345,7 @@
         <v>21.29</v>
       </c>
       <c r="H739" t="n">
-        <v>0.2265085273092215</v>
+        <v>0.2195769512431107</v>
       </c>
       <c r="I739" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>42.39</v>
       </c>
       <c r="H740" t="n">
-        <v>0.05902933954013356</v>
+        <v>0.06539799261355017</v>
       </c>
       <c r="I740" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>12.04</v>
       </c>
       <c r="H741" t="n">
-        <v>0.1828903125528313</v>
+        <v>0.1910944141250944</v>
       </c>
       <c r="I741" t="inlineStr">
         <is>
@@ -23438,7 +23438,7 @@
         <v>18.46</v>
       </c>
       <c r="H742" t="n">
-        <v>0.06462895153601955</v>
+        <v>0.06424883222860445</v>
       </c>
       <c r="I742" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>3.49</v>
       </c>
       <c r="H743" t="n">
-        <v>0.05653777004474148</v>
+        <v>0.06719929661538337</v>
       </c>
       <c r="I743" t="inlineStr">
         <is>
@@ -23500,7 +23500,7 @@
         <v>12.79</v>
       </c>
       <c r="H744" t="n">
-        <v>0.0578955769065651</v>
+        <v>0.0675410750443407</v>
       </c>
       <c r="I744" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>32.16</v>
       </c>
       <c r="H745" t="n">
-        <v>0.06662071360821298</v>
+        <v>0.05174546635047861</v>
       </c>
       <c r="I745" t="inlineStr">
         <is>
@@ -23562,7 +23562,7 @@
         <v>14.34</v>
       </c>
       <c r="H746" t="n">
-        <v>0.2149666214655101</v>
+        <v>0.2103025508224245</v>
       </c>
       <c r="I746" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>4.39</v>
       </c>
       <c r="H747" t="n">
-        <v>0.134818070226486</v>
+        <v>0.1331084843841047</v>
       </c>
       <c r="I747" t="inlineStr">
         <is>
@@ -23624,7 +23624,7 @@
         <v>42.75</v>
       </c>
       <c r="H748" t="n">
-        <v>0.2003032263469872</v>
+        <v>0.1979167574633015</v>
       </c>
       <c r="I748" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>23.61</v>
       </c>
       <c r="H749" t="n">
-        <v>0.2292874574819078</v>
+        <v>0.2161916739594303</v>
       </c>
       <c r="I749" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>75.38</v>
       </c>
       <c r="H750" t="n">
-        <v>0.05479717783794191</v>
+        <v>0.05133849585132733</v>
       </c>
       <c r="I750" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>37.27</v>
       </c>
       <c r="H751" t="n">
-        <v>0.1032405764035715</v>
+        <v>0.09106724562480772</v>
       </c>
       <c r="I751" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>37.48</v>
       </c>
       <c r="H752" t="n">
-        <v>0.01418244660708845</v>
+        <v>0.01737586414915382</v>
       </c>
       <c r="I752" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>0.64</v>
       </c>
       <c r="H753" t="n">
-        <v>0.1092522952936609</v>
+        <v>0.104206578201867</v>
       </c>
       <c r="I753" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>12.27</v>
       </c>
       <c r="H754" t="n">
-        <v>0.2189752611270946</v>
+        <v>0.2137993172848105</v>
       </c>
       <c r="I754" t="inlineStr">
         <is>
@@ -23841,7 +23841,7 @@
         <v>7.22</v>
       </c>
       <c r="H755" t="n">
-        <v>0.1796865687894273</v>
+        <v>0.1809075458620704</v>
       </c>
       <c r="I755" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>0.38</v>
       </c>
       <c r="H756" t="n">
-        <v>0.1048155794542989</v>
+        <v>0.09980477659055653</v>
       </c>
       <c r="I756" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>3.95</v>
       </c>
       <c r="H757" t="n">
-        <v>0.127751545564726</v>
+        <v>0.1260985959204792</v>
       </c>
       <c r="I757" t="inlineStr">
         <is>
@@ -23934,7 +23934,7 @@
         <v>7.5</v>
       </c>
       <c r="H758" t="n">
-        <v>0.08544300581308806</v>
+        <v>0.07917670818208999</v>
       </c>
       <c r="I758" t="inlineStr">
         <is>
@@ -23965,7 +23965,7 @@
         <v>4.85</v>
       </c>
       <c r="H759" t="n">
-        <v>0.1295615776182586</v>
+        <v>0.1183907719099944</v>
       </c>
       <c r="I759" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>2.34</v>
       </c>
       <c r="H760" t="n">
-        <v>0.1824593237622517</v>
+        <v>0.1818519693793015</v>
       </c>
       <c r="I760" t="inlineStr">
         <is>
@@ -24027,7 +24027,7 @@
         <v>7.02</v>
       </c>
       <c r="H761" t="n">
-        <v>0.004478473014125406</v>
+        <v>0.01149173373268342</v>
       </c>
       <c r="I761" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>19.94</v>
       </c>
       <c r="H762" t="n">
-        <v>0.2386202810162665</v>
+        <v>0.2304247882255918</v>
       </c>
       <c r="I762" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>12.03</v>
       </c>
       <c r="H763" t="n">
-        <v>-0.01568490162372693</v>
+        <v>-0.01875461506203424</v>
       </c>
       <c r="I763" t="inlineStr">
         <is>
@@ -24120,7 +24120,7 @@
         <v>23.01</v>
       </c>
       <c r="H764" t="n">
-        <v>0.2185811267191218</v>
+        <v>0.2127322737838511</v>
       </c>
       <c r="I764" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>31.65</v>
       </c>
       <c r="H765" t="n">
-        <v>0.1934592695624223</v>
+        <v>0.1827812283841033</v>
       </c>
       <c r="I765" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>22.55</v>
       </c>
       <c r="H766" t="n">
-        <v>0.2386938109245562</v>
+        <v>0.2302481472016454</v>
       </c>
       <c r="I766" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>23.41</v>
       </c>
       <c r="H767" t="n">
-        <v>-0.01139322637520879</v>
+        <v>-0.01682233311327874</v>
       </c>
       <c r="I767" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>1.65</v>
       </c>
       <c r="H768" t="n">
-        <v>0.1164006570099775</v>
+        <v>0.1085270939429543</v>
       </c>
       <c r="I768" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>18.05</v>
       </c>
       <c r="H769" t="n">
-        <v>0.222072468810611</v>
+        <v>0.2177641950329324</v>
       </c>
       <c r="I769" t="inlineStr">
         <is>
@@ -24306,7 +24306,7 @@
         <v>35.71</v>
       </c>
       <c r="H770" t="n">
-        <v>0.227169793291997</v>
+        <v>0.2215949283980672</v>
       </c>
       <c r="I770" t="inlineStr">
         <is>
@@ -24337,7 +24337,7 @@
         <v>135.45</v>
       </c>
       <c r="H771" t="n">
-        <v>0.04176036987853271</v>
+        <v>0.02880474559853019</v>
       </c>
       <c r="I771" t="inlineStr">
         <is>
@@ -24368,7 +24368,7 @@
         <v>77.68000000000001</v>
       </c>
       <c r="H772" t="n">
-        <v>0.138242493741411</v>
+        <v>0.1286316051066942</v>
       </c>
       <c r="I772" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>4.47</v>
       </c>
       <c r="H773" t="n">
-        <v>0.06432158955271794</v>
+        <v>0.06115293227219143</v>
       </c>
       <c r="I773" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>6.46</v>
       </c>
       <c r="H774" t="n">
-        <v>0.1121098366508108</v>
+        <v>0.1039172185907361</v>
       </c>
       <c r="I774" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>8.279999999999999</v>
       </c>
       <c r="H775" t="n">
-        <v>0.1255726788605492</v>
+        <v>0.1217886257194608</v>
       </c>
       <c r="I775" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>7.45</v>
       </c>
       <c r="H776" t="n">
-        <v>0.1378226941918124</v>
+        <v>0.1363049533101458</v>
       </c>
       <c r="I776" t="inlineStr">
         <is>
@@ -24523,7 +24523,7 @@
         <v>35.68</v>
       </c>
       <c r="H777" t="n">
-        <v>0.1394106303661599</v>
+        <v>0.1306374470709696</v>
       </c>
       <c r="I777" t="inlineStr">
         <is>
@@ -24554,7 +24554,7 @@
         <v>15.96</v>
       </c>
       <c r="H778" t="n">
-        <v>0.163986925902579</v>
+        <v>0.1725740647921479</v>
       </c>
       <c r="I778" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>28.15</v>
       </c>
       <c r="H779" t="n">
-        <v>0.2268935759964054</v>
+        <v>0.214783616595534</v>
       </c>
       <c r="I779" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>13.82</v>
       </c>
       <c r="H780" t="n">
-        <v>0.2212278200293585</v>
+        <v>0.2152323558335463</v>
       </c>
       <c r="I780" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>6.76</v>
       </c>
       <c r="H781" t="n">
-        <v>0.0683409461706892</v>
+        <v>0.06809129327586927</v>
       </c>
       <c r="I781" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>4.49</v>
       </c>
       <c r="H782" t="n">
-        <v>0.1666980742576903</v>
+        <v>0.1678360733604281</v>
       </c>
       <c r="I782" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>16.98</v>
       </c>
       <c r="H783" t="n">
-        <v>0.1366396588089894</v>
+        <v>0.1319839124755441</v>
       </c>
       <c r="I783" t="inlineStr">
         <is>
@@ -24740,7 +24740,7 @@
         <v>4.46</v>
       </c>
       <c r="H784" t="n">
-        <v>0.1066445330930098</v>
+        <v>0.1002684239173599</v>
       </c>
       <c r="I784" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>14.46</v>
       </c>
       <c r="H785" t="n">
-        <v>0.1352634643448158</v>
+        <v>0.1450177722002683</v>
       </c>
       <c r="I785" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>35.87</v>
       </c>
       <c r="H786" t="n">
-        <v>0.02705521847401471</v>
+        <v>0.03673553299900334</v>
       </c>
       <c r="I786" t="inlineStr">
         <is>
@@ -24833,7 +24833,7 @@
         <v>0.55</v>
       </c>
       <c r="H787" t="n">
-        <v>0.1077921261797188</v>
+        <v>0.1052792836063176</v>
       </c>
       <c r="I787" t="inlineStr">
         <is>
@@ -24864,11 +24864,11 @@
         <v>74.14</v>
       </c>
       <c r="H788" t="n">
-        <v>0.01227230661812861</v>
+        <v>-0.0006802757245494284</v>
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Suspicious</t>
         </is>
       </c>
     </row>
@@ -24895,7 +24895,7 @@
         <v>11.36</v>
       </c>
       <c r="H789" t="n">
-        <v>0.2316896731420198</v>
+        <v>0.2253413471402033</v>
       </c>
       <c r="I789" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>11.11</v>
       </c>
       <c r="H790" t="n">
-        <v>0.1198659761256474</v>
+        <v>0.1264724725813394</v>
       </c>
       <c r="I790" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>23.1</v>
       </c>
       <c r="H791" t="n">
-        <v>0.09453004101736562</v>
+        <v>0.1000150821028351</v>
       </c>
       <c r="I791" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>11</v>
       </c>
       <c r="H792" t="n">
-        <v>0.2091037183693084</v>
+        <v>0.2046923786931713</v>
       </c>
       <c r="I792" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>9.67</v>
       </c>
       <c r="H793" t="n">
-        <v>-0.004055212639172967</v>
+        <v>-0.0126111664488332</v>
       </c>
       <c r="I793" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>51.13</v>
       </c>
       <c r="H794" t="n">
-        <v>0.2019760761282808</v>
+        <v>0.1955906058733182</v>
       </c>
       <c r="I794" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>40.25</v>
       </c>
       <c r="H795" t="n">
-        <v>0.2140974905286489</v>
+        <v>0.2061925854309303</v>
       </c>
       <c r="I795" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>18.38</v>
       </c>
       <c r="H796" t="n">
-        <v>0.2192599550156943</v>
+        <v>0.2123191668912817</v>
       </c>
       <c r="I796" t="inlineStr">
         <is>
@@ -25143,7 +25143,7 @@
         <v>22.78</v>
       </c>
       <c r="H797" t="n">
-        <v>0.2262212631789997</v>
+        <v>0.2193777412457064</v>
       </c>
       <c r="I797" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>135.56</v>
       </c>
       <c r="H798" t="n">
-        <v>0.07275025491539</v>
+        <v>0.05935965559111589</v>
       </c>
       <c r="I798" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>35.01</v>
       </c>
       <c r="H799" t="n">
-        <v>0.1909772214036217</v>
+        <v>0.1812752312592731</v>
       </c>
       <c r="I799" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>19.78</v>
       </c>
       <c r="H800" t="n">
-        <v>0.1356850344782112</v>
+        <v>0.137499213918695</v>
       </c>
       <c r="I800" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>36.19</v>
       </c>
       <c r="H801" t="n">
-        <v>0.1898538713173173</v>
+        <v>0.181178192126851</v>
       </c>
       <c r="I801" t="inlineStr">
         <is>
@@ -25298,7 +25298,7 @@
         <v>10.24</v>
       </c>
       <c r="H802" t="n">
-        <v>0.1365656632010565</v>
+        <v>0.1327869563921912</v>
       </c>
       <c r="I802" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>20.46</v>
       </c>
       <c r="H803" t="n">
-        <v>0.0722138516901385</v>
+        <v>0.08886503172832105</v>
       </c>
       <c r="I803" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>38.82</v>
       </c>
       <c r="H804" t="n">
-        <v>0.08338208032520211</v>
+        <v>0.0838963143322905</v>
       </c>
       <c r="I804" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>77.81999999999999</v>
       </c>
       <c r="H805" t="n">
-        <v>0.01253834492709927</v>
+        <v>0.01184241437539191</v>
       </c>
       <c r="I805" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>24.35</v>
       </c>
       <c r="H806" t="n">
-        <v>0.2175527682842853</v>
+        <v>0.2127468265923371</v>
       </c>
       <c r="I806" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>5.03</v>
       </c>
       <c r="H807" t="n">
-        <v>0.04195871575755961</v>
+        <v>0.04173504489963542</v>
       </c>
       <c r="I807" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>10.8</v>
       </c>
       <c r="H808" t="n">
-        <v>0.2157715322871958</v>
+        <v>0.2104633038797055</v>
       </c>
       <c r="I808" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>36.4</v>
       </c>
       <c r="H809" t="n">
-        <v>0.0548009711966162</v>
+        <v>0.04354876716340583</v>
       </c>
       <c r="I809" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>4.24</v>
       </c>
       <c r="H810" t="n">
-        <v>0.213354223544695</v>
+        <v>0.2130998963039261</v>
       </c>
       <c r="I810" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>36.68</v>
       </c>
       <c r="H811" t="n">
-        <v>0.2042771831991703</v>
+        <v>0.2011992716305144</v>
       </c>
       <c r="I811" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>37.16</v>
       </c>
       <c r="H812" t="n">
-        <v>0.2168546766111181</v>
+        <v>0.21362474387653</v>
       </c>
       <c r="I812" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>9.35</v>
       </c>
       <c r="H813" t="n">
-        <v>0.1361242852974732</v>
+        <v>0.1328847532925327</v>
       </c>
       <c r="I813" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>178.43</v>
       </c>
       <c r="H814" t="n">
-        <v>0.01242299025668248</v>
+        <v>0.02332796507032708</v>
       </c>
       <c r="I814" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>107.77</v>
       </c>
       <c r="H815" t="n">
-        <v>0.1134442242812496</v>
+        <v>0.09224356353705665</v>
       </c>
       <c r="I815" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>5.79</v>
       </c>
       <c r="H816" t="n">
-        <v>0.2020062934351803</v>
+        <v>0.1926482184158205</v>
       </c>
       <c r="I816" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>22.3</v>
       </c>
       <c r="H817" t="n">
-        <v>-0.001579628026706081</v>
+        <v>-0.01516370207467288</v>
       </c>
       <c r="I817" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>32.37</v>
       </c>
       <c r="H818" t="n">
-        <v>0.2198606348213246</v>
+        <v>0.2128463605228048</v>
       </c>
       <c r="I818" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>99.83</v>
       </c>
       <c r="H819" t="n">
-        <v>0.03078036072387713</v>
+        <v>0.02387660513814349</v>
       </c>
       <c r="I819" t="inlineStr">
         <is>
@@ -25856,7 +25856,7 @@
         <v>66.95</v>
       </c>
       <c r="H820" t="n">
-        <v>0.0809582616112442</v>
+        <v>0.07540357607924597</v>
       </c>
       <c r="I820" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>22.94</v>
       </c>
       <c r="H821" t="n">
-        <v>0.2386938109245562</v>
+        <v>0.2294271903789553</v>
       </c>
       <c r="I821" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>1.45</v>
       </c>
       <c r="H822" t="n">
-        <v>0.1055102010006728</v>
+        <v>0.104828848339045</v>
       </c>
       <c r="I822" t="inlineStr">
         <is>
@@ -25949,7 +25949,7 @@
         <v>49.05</v>
       </c>
       <c r="H823" t="n">
-        <v>0.1127520219822441</v>
+        <v>0.1229045210045994</v>
       </c>
       <c r="I823" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>29.37</v>
       </c>
       <c r="H824" t="n">
-        <v>0.1473208292987854</v>
+        <v>0.1479438113554521</v>
       </c>
       <c r="I824" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>44.73</v>
       </c>
       <c r="H825" t="n">
-        <v>0.2177610897728181</v>
+        <v>0.2135155231243545</v>
       </c>
       <c r="I825" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>8.81</v>
       </c>
       <c r="H826" t="n">
-        <v>0.2142352028619525</v>
+        <v>0.2070021414573772</v>
       </c>
       <c r="I826" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>14.5</v>
       </c>
       <c r="H827" t="n">
-        <v>0.129556550343781</v>
+        <v>0.1263147445093101</v>
       </c>
       <c r="I827" t="inlineStr">
         <is>
@@ -26104,7 +26104,7 @@
         <v>22.62</v>
       </c>
       <c r="H828" t="n">
-        <v>0.2184446228376936</v>
+        <v>0.2127632824114293</v>
       </c>
       <c r="I828" t="inlineStr">
         <is>
@@ -26135,7 +26135,7 @@
         <v>12.66</v>
       </c>
       <c r="H829" t="n">
-        <v>0.1095910624460629</v>
+        <v>0.1074326766432141</v>
       </c>
       <c r="I829" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>27.14</v>
       </c>
       <c r="H830" t="n">
-        <v>0.0389634632451098</v>
+        <v>0.05012697852727555</v>
       </c>
       <c r="I830" t="inlineStr">
         <is>
@@ -26197,7 +26197,7 @@
         <v>23.19</v>
       </c>
       <c r="H831" t="n">
-        <v>0.2184795187289126</v>
+        <v>0.2127322737838511</v>
       </c>
       <c r="I831" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>10.34</v>
       </c>
       <c r="H832" t="n">
-        <v>0.1286995281845388</v>
+        <v>0.1248658794749996</v>
       </c>
       <c r="I832" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>11.39</v>
       </c>
       <c r="H833" t="n">
-        <v>0.1197763122452429</v>
+        <v>0.1197639607952447</v>
       </c>
       <c r="I833" t="inlineStr">
         <is>
@@ -26290,7 +26290,7 @@
         <v>5.82</v>
       </c>
       <c r="H834" t="n">
-        <v>0.1472788838319319</v>
+        <v>0.140274801359482</v>
       </c>
       <c r="I834" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>25.05</v>
       </c>
       <c r="H835" t="n">
-        <v>0.2377602168001333</v>
+        <v>0.22940567848685</v>
       </c>
       <c r="I835" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>39.63</v>
       </c>
       <c r="H836" t="n">
-        <v>0.09848014306405262</v>
+        <v>0.08561849883488981</v>
       </c>
       <c r="I836" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>9.24</v>
       </c>
       <c r="H837" t="n">
-        <v>0.1296655755181075</v>
+        <v>0.1306177437228601</v>
       </c>
       <c r="I837" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>23.22</v>
       </c>
       <c r="H838" t="n">
-        <v>0.03585300518804069</v>
+        <v>0.03183238925153864</v>
       </c>
       <c r="I838" t="inlineStr">
         <is>
@@ -26445,7 +26445,7 @@
         <v>19.43</v>
       </c>
       <c r="H839" t="n">
-        <v>0.2198545953208524</v>
+        <v>0.2127157326772328</v>
       </c>
       <c r="I839" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>7.58</v>
       </c>
       <c r="H840" t="n">
-        <v>0.04170811941125641</v>
+        <v>0.04328209579618181</v>
       </c>
       <c r="I840" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>42.48</v>
       </c>
       <c r="H841" t="n">
-        <v>0.2102620895702151</v>
+        <v>0.2103451036865564</v>
       </c>
       <c r="I841" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>8.029999999999999</v>
       </c>
       <c r="H842" t="n">
-        <v>0.0349081937123864</v>
+        <v>0.02955337954912196</v>
       </c>
       <c r="I842" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>4.77</v>
       </c>
       <c r="H843" t="n">
-        <v>0.02940810472001787</v>
+        <v>0.02805097807800883</v>
       </c>
       <c r="I843" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>26.31</v>
       </c>
       <c r="H844" t="n">
-        <v>0.07831967831538356</v>
+        <v>0.0807169933224865</v>
       </c>
       <c r="I844" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>7.6</v>
       </c>
       <c r="H845" t="n">
-        <v>0.09957169548408618</v>
+        <v>0.08976171202283345</v>
       </c>
       <c r="I845" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>2.9</v>
       </c>
       <c r="H846" t="n">
-        <v>0.07695986182391812</v>
+        <v>0.06687884877135819</v>
       </c>
       <c r="I846" t="inlineStr">
         <is>
@@ -26693,7 +26693,7 @@
         <v>107.61</v>
       </c>
       <c r="H847" t="n">
-        <v>0.115480309390063</v>
+        <v>0.1015309014683066</v>
       </c>
       <c r="I847" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>29.24</v>
       </c>
       <c r="H848" t="n">
-        <v>-0.006279575903030743</v>
+        <v>-0.01509251222764563</v>
       </c>
       <c r="I848" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>10.1</v>
       </c>
       <c r="H849" t="n">
-        <v>0.1870388160586636</v>
+        <v>0.1888022448403428</v>
       </c>
       <c r="I849" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>33.17</v>
       </c>
       <c r="H850" t="n">
-        <v>0.1096580784737334</v>
+        <v>0.1107170510093229</v>
       </c>
       <c r="I850" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>41.64</v>
       </c>
       <c r="H851" t="n">
-        <v>0.2116008705372703</v>
+        <v>0.2102883410860072</v>
       </c>
       <c r="I851" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>25.79</v>
       </c>
       <c r="H852" t="n">
-        <v>0.05542135253787006</v>
+        <v>0.04447456881618428</v>
       </c>
       <c r="I852" t="inlineStr">
         <is>
@@ -26879,7 +26879,7 @@
         <v>1.51</v>
       </c>
       <c r="H853" t="n">
-        <v>0.1262265251773894</v>
+        <v>0.1219951009808704</v>
       </c>
       <c r="I853" t="inlineStr">
         <is>
@@ -26910,7 +26910,7 @@
         <v>13.62</v>
       </c>
       <c r="H854" t="n">
-        <v>0.119259714980879</v>
+        <v>0.110545353284028</v>
       </c>
       <c r="I854" t="inlineStr">
         <is>
@@ -26941,7 +26941,7 @@
         <v>33.91</v>
       </c>
       <c r="H855" t="n">
-        <v>0.02350531129301903</v>
+        <v>0.03173561864928331</v>
       </c>
       <c r="I855" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         <v>28.16</v>
       </c>
       <c r="H856" t="n">
-        <v>0.1087428553974611</v>
+        <v>0.09508501166034411</v>
       </c>
       <c r="I856" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>48.16</v>
       </c>
       <c r="H857" t="n">
-        <v>0.164151861138966</v>
+        <v>0.164974066719586</v>
       </c>
       <c r="I857" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>19.47</v>
       </c>
       <c r="H858" t="n">
-        <v>0.2272567145073509</v>
+        <v>0.2236233810082547</v>
       </c>
       <c r="I858" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>48.32</v>
       </c>
       <c r="H859" t="n">
-        <v>0.0218449330306798</v>
+        <v>0.00723124613739079</v>
       </c>
       <c r="I859" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>2.1</v>
       </c>
       <c r="H860" t="n">
-        <v>-0.0107597657194628</v>
+        <v>-0.01445722448573328</v>
       </c>
       <c r="I860" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>18.24</v>
       </c>
       <c r="H861" t="n">
-        <v>0.1616376958686225</v>
+        <v>0.1717913426173934</v>
       </c>
       <c r="I861" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>15.12</v>
       </c>
       <c r="H862" t="n">
-        <v>0.04161672284989593</v>
+        <v>0.0435659317650714</v>
       </c>
       <c r="I862" t="inlineStr">
         <is>
@@ -27189,7 +27189,7 @@
         <v>41.39</v>
       </c>
       <c r="H863" t="n">
-        <v>0.2003265667842801</v>
+        <v>0.1985339478862387</v>
       </c>
       <c r="I863" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>2.75</v>
       </c>
       <c r="H864" t="n">
-        <v>0.1274354893944859</v>
+        <v>0.1242699974082885</v>
       </c>
       <c r="I864" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>134.93</v>
       </c>
       <c r="H865" t="n">
-        <v>0.04968203521730319</v>
+        <v>0.05343587258869453</v>
       </c>
       <c r="I865" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>6.23</v>
       </c>
       <c r="H866" t="n">
-        <v>0.1182125154712957</v>
+        <v>0.1117273583166768</v>
       </c>
       <c r="I866" t="inlineStr">
         <is>
@@ -27313,7 +27313,7 @@
         <v>77.62</v>
       </c>
       <c r="H867" t="n">
-        <v>0.05501355076996894</v>
+        <v>0.05383544668868445</v>
       </c>
       <c r="I867" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>43.27</v>
       </c>
       <c r="H868" t="n">
-        <v>0.2197848694822151</v>
+        <v>0.2155891587151554</v>
       </c>
       <c r="I868" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>40.59</v>
       </c>
       <c r="H869" t="n">
-        <v>0.2236349774424119</v>
+        <v>0.21685706116136</v>
       </c>
       <c r="I869" t="inlineStr">
         <is>
@@ -27406,7 +27406,7 @@
         <v>10.53</v>
       </c>
       <c r="H870" t="n">
-        <v>0.2127730998365758</v>
+        <v>0.2118969413909106</v>
       </c>
       <c r="I870" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>2.63</v>
       </c>
       <c r="H871" t="n">
-        <v>0.1304747696390363</v>
+        <v>0.1272984670262912</v>
       </c>
       <c r="I871" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>13.68</v>
       </c>
       <c r="H872" t="n">
-        <v>0.05063941745624878</v>
+        <v>0.05033571965953199</v>
       </c>
       <c r="I872" t="inlineStr">
         <is>
@@ -27499,7 +27499,7 @@
         <v>37.4</v>
       </c>
       <c r="H873" t="n">
-        <v>0.07889621238914735</v>
+        <v>0.07631508614870919</v>
       </c>
       <c r="I873" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>10.68</v>
       </c>
       <c r="H874" t="n">
-        <v>0.1443505879429078</v>
+        <v>0.148350019292506</v>
       </c>
       <c r="I874" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>6.62</v>
       </c>
       <c r="H875" t="n">
-        <v>0.05948495107398466</v>
+        <v>0.05736915946360932</v>
       </c>
       <c r="I875" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>19</v>
       </c>
       <c r="H876" t="n">
-        <v>0.227611213592585</v>
+        <v>0.2226710168919908</v>
       </c>
       <c r="I876" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>51.84</v>
       </c>
       <c r="H877" t="n">
-        <v>0.05552758857104645</v>
+        <v>0.06777044401539134</v>
       </c>
       <c r="I877" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>48.28</v>
       </c>
       <c r="H878" t="n">
-        <v>0.2035670228873754</v>
+        <v>0.2002305760343702</v>
       </c>
       <c r="I878" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         <v>22.1</v>
       </c>
       <c r="H879" t="n">
-        <v>0.1043189692950803</v>
+        <v>0.09277731965336966</v>
       </c>
       <c r="I879" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>25.73</v>
       </c>
       <c r="H880" t="n">
-        <v>0.2380141468315599</v>
+        <v>0.2288475290437168</v>
       </c>
       <c r="I880" t="inlineStr">
         <is>
@@ -27747,7 +27747,7 @@
         <v>19.74</v>
       </c>
       <c r="H881" t="n">
-        <v>0.1346649114267187</v>
+        <v>0.1471967654399563</v>
       </c>
       <c r="I881" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>114.3</v>
       </c>
       <c r="H882" t="n">
-        <v>0.107018052836655</v>
+        <v>0.09627833568085287</v>
       </c>
       <c r="I882" t="inlineStr">
         <is>
@@ -27809,7 +27809,7 @@
         <v>3.74</v>
       </c>
       <c r="H883" t="n">
-        <v>0.1225553633485623</v>
+        <v>0.1151506100733998</v>
       </c>
       <c r="I883" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>11.74</v>
       </c>
       <c r="H884" t="n">
-        <v>0.1633367371559047</v>
+        <v>0.1739126973690454</v>
       </c>
       <c r="I884" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>29.3</v>
       </c>
       <c r="H885" t="n">
-        <v>0.2326114497881224</v>
+        <v>0.2267738717028085</v>
       </c>
       <c r="I885" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>3.27</v>
       </c>
       <c r="H886" t="n">
-        <v>0.132580865406671</v>
+        <v>0.1291379097642998</v>
       </c>
       <c r="I886" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>11.38</v>
       </c>
       <c r="H887" t="n">
-        <v>0.06693479052580775</v>
+        <v>0.08046764505279302</v>
       </c>
       <c r="I887" t="inlineStr">
         <is>
@@ -27964,7 +27964,7 @@
         <v>67.22</v>
       </c>
       <c r="H888" t="n">
-        <v>0.05339587285299652</v>
+        <v>0.04783421247805009</v>
       </c>
       <c r="I888" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45.97</v>
       </c>
       <c r="H889" t="n">
-        <v>0.2085340856756634</v>
+        <v>0.202011994451563</v>
       </c>
       <c r="I889" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>13.75</v>
       </c>
       <c r="H890" t="n">
-        <v>0.225130275488065</v>
+        <v>0.2219344144133619</v>
       </c>
       <c r="I890" t="inlineStr">
         <is>
@@ -28057,7 +28057,7 @@
         <v>2.39</v>
       </c>
       <c r="H891" t="n">
-        <v>0.1212432573734471</v>
+        <v>0.1171020889841616</v>
       </c>
       <c r="I891" t="inlineStr">
         <is>
@@ -28088,7 +28088,7 @@
         <v>5.86</v>
       </c>
       <c r="H892" t="n">
-        <v>0.2083320273095813</v>
+        <v>0.1988272358442583</v>
       </c>
       <c r="I892" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>15.55</v>
       </c>
       <c r="H893" t="n">
-        <v>0.2220188148898864</v>
+        <v>0.2165033165514093</v>
       </c>
       <c r="I893" t="inlineStr">
         <is>
@@ -28150,7 +28150,7 @@
         <v>22.69</v>
       </c>
       <c r="H894" t="n">
-        <v>0.1134671934977647</v>
+        <v>0.1111255866593736</v>
       </c>
       <c r="I894" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>30.82</v>
       </c>
       <c r="H895" t="n">
-        <v>0.2302651507205871</v>
+        <v>0.2234712541551665</v>
       </c>
       <c r="I895" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>16.29</v>
       </c>
       <c r="H896" t="n">
-        <v>0.2260636683300496</v>
+        <v>0.2190300881720519</v>
       </c>
       <c r="I896" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>7.84</v>
       </c>
       <c r="H897" t="n">
-        <v>0.07570767782165611</v>
+        <v>0.08728977293517559</v>
       </c>
       <c r="I897" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>19.52</v>
       </c>
       <c r="H898" t="n">
-        <v>0.2279286678259131</v>
+        <v>0.2236233810082547</v>
       </c>
       <c r="I898" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>13.68</v>
       </c>
       <c r="H899" t="n">
-        <v>0.1531235463362453</v>
+        <v>0.1453379274460707</v>
       </c>
       <c r="I899" t="inlineStr">
         <is>
@@ -28336,7 +28336,7 @@
         <v>41.72</v>
       </c>
       <c r="H900" t="n">
-        <v>0.200450198907177</v>
+        <v>0.1981620922000246</v>
       </c>
       <c r="I900" t="inlineStr">
         <is>
@@ -28367,7 +28367,7 @@
         <v>159.07</v>
       </c>
       <c r="H901" t="n">
-        <v>-0.0457570400827968</v>
+        <v>-0.05161543830901805</v>
       </c>
       <c r="I901" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>24.6</v>
       </c>
       <c r="H902" t="n">
-        <v>0.2387038936066696</v>
+        <v>0.2289138917311257</v>
       </c>
       <c r="I902" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>55.15</v>
       </c>
       <c r="H903" t="n">
-        <v>0.2083674788662824</v>
+        <v>0.1969521670437948</v>
       </c>
       <c r="I903" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>49.55</v>
       </c>
       <c r="H904" t="n">
-        <v>0.1122727138019305</v>
+        <v>0.1071659687070878</v>
       </c>
       <c r="I904" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>30.53</v>
       </c>
       <c r="H905" t="n">
-        <v>0.2236617518541856</v>
+        <v>0.2096089205106104</v>
       </c>
       <c r="I905" t="inlineStr">
         <is>
@@ -28522,7 +28522,7 @@
         <v>22.23</v>
       </c>
       <c r="H906" t="n">
-        <v>0.156734925452392</v>
+        <v>0.1664198415511092</v>
       </c>
       <c r="I906" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>20.68</v>
       </c>
       <c r="H907" t="n">
-        <v>0.2269579463171945</v>
+        <v>0.2196211661189677</v>
       </c>
       <c r="I907" t="inlineStr">
         <is>
@@ -28584,7 +28584,7 @@
         <v>6.68</v>
       </c>
       <c r="H908" t="n">
-        <v>-0.007269032488386729</v>
+        <v>-0.01706864829854393</v>
       </c>
       <c r="I908" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44.19</v>
       </c>
       <c r="H909" t="n">
-        <v>0.1998446446959316</v>
+        <v>0.1954737158140755</v>
       </c>
       <c r="I909" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>38.08</v>
       </c>
       <c r="H910" t="n">
-        <v>0.2054725915771147</v>
+        <v>0.1997659749448827</v>
       </c>
       <c r="I910" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>22.11</v>
       </c>
       <c r="H911" t="n">
-        <v>0.2390736390390147</v>
+        <v>0.2296998004876843</v>
       </c>
       <c r="I911" t="inlineStr">
         <is>
@@ -28708,7 +28708,7 @@
         <v>27.51</v>
       </c>
       <c r="H912" t="n">
-        <v>0.2273282435191875</v>
+        <v>0.2158034838293545</v>
       </c>
       <c r="I912" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>33.78</v>
       </c>
       <c r="H913" t="n">
-        <v>0.108891132154039</v>
+        <v>0.09590348479294397</v>
       </c>
       <c r="I913" t="inlineStr">
         <is>
@@ -28770,7 +28770,7 @@
         <v>37.9</v>
       </c>
       <c r="H914" t="n">
-        <v>0.1066189437442365</v>
+        <v>0.1105467690978832</v>
       </c>
       <c r="I914" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>0.8</v>
       </c>
       <c r="H915" t="n">
-        <v>0.04775298705529207</v>
+        <v>0.05780127286598769</v>
       </c>
       <c r="I915" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>9.23</v>
       </c>
       <c r="H916" t="n">
-        <v>0.1492655505187557</v>
+        <v>0.1434117427492259</v>
       </c>
       <c r="I916" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>22.05</v>
       </c>
       <c r="H917" t="n">
-        <v>0.2379066615832995</v>
+        <v>0.2299668322610469</v>
       </c>
       <c r="I917" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>1.45</v>
       </c>
       <c r="H918" t="n">
-        <v>0.0975641658112395</v>
+        <v>0.09059100681185561</v>
       </c>
       <c r="I918" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>15.05</v>
       </c>
       <c r="H919" t="n">
-        <v>0.142340799286814</v>
+        <v>0.1442544142260307</v>
       </c>
       <c r="I919" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>13.56</v>
       </c>
       <c r="H920" t="n">
-        <v>0.225048309106598</v>
+        <v>0.2153745768095912</v>
       </c>
       <c r="I920" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>20.6</v>
       </c>
       <c r="H921" t="n">
-        <v>0.07056947428372751</v>
+        <v>0.07445759448216405</v>
       </c>
       <c r="I921" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>9.960000000000001</v>
       </c>
       <c r="H922" t="n">
-        <v>0.005756636966694373</v>
+        <v>0.0140917584526935</v>
       </c>
       <c r="I922" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>14.49</v>
       </c>
       <c r="H923" t="n">
-        <v>0.2365909623337444</v>
+        <v>0.2277658487528469</v>
       </c>
       <c r="I923" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>23.55</v>
       </c>
       <c r="H924" t="n">
-        <v>0.09486983638338964</v>
+        <v>0.09958708505376512</v>
       </c>
       <c r="I924" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45.61</v>
       </c>
       <c r="H925" t="n">
-        <v>0.2074288058406087</v>
+        <v>0.203310885349685</v>
       </c>
       <c r="I925" t="inlineStr">
         <is>
@@ -29142,7 +29142,7 @@
         <v>13.01</v>
       </c>
       <c r="H926" t="n">
-        <v>0.05911737177507537</v>
+        <v>0.05786347500189792</v>
       </c>
       <c r="I926" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>11.9</v>
       </c>
       <c r="H927" t="n">
-        <v>0.09817855397460173</v>
+        <v>0.1017609490386353</v>
       </c>
       <c r="I927" t="inlineStr">
         <is>
@@ -29204,7 +29204,7 @@
         <v>3.03</v>
       </c>
       <c r="H928" t="n">
-        <v>0.2020116852515523</v>
+        <v>0.2010168006315468</v>
       </c>
       <c r="I928" t="inlineStr">
         <is>
@@ -29235,7 +29235,7 @@
         <v>7.59</v>
       </c>
       <c r="H929" t="n">
-        <v>0.1284794577072652</v>
+        <v>0.1279613048409022</v>
       </c>
       <c r="I929" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>12.8</v>
       </c>
       <c r="H930" t="n">
-        <v>0.2204549468185455</v>
+        <v>0.2143728460951811</v>
       </c>
       <c r="I930" t="inlineStr">
         <is>
@@ -29297,7 +29297,7 @@
         <v>39.82</v>
       </c>
       <c r="H931" t="n">
-        <v>0.2240881863725855</v>
+        <v>0.2168492040381011</v>
       </c>
       <c r="I931" t="inlineStr">
         <is>
@@ -29328,7 +29328,7 @@
         <v>172.41</v>
       </c>
       <c r="H932" t="n">
-        <v>-0.02347235673838144</v>
+        <v>-0.02615189914003924</v>
       </c>
       <c r="I932" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>26.69</v>
       </c>
       <c r="H933" t="n">
-        <v>0.2271019088804044</v>
+        <v>0.2142760854693748</v>
       </c>
       <c r="I933" t="inlineStr">
         <is>
@@ -29390,7 +29390,7 @@
         <v>10.87</v>
       </c>
       <c r="H934" t="n">
-        <v>0.0490140514142321</v>
+        <v>0.03867388388221515</v>
       </c>
       <c r="I934" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>60.64</v>
       </c>
       <c r="H935" t="n">
-        <v>0.1893863079945625</v>
+        <v>0.1782052855929182</v>
       </c>
       <c r="I935" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>26.54</v>
       </c>
       <c r="H936" t="n">
-        <v>0.2250363826194963</v>
+        <v>0.2190281114469853</v>
       </c>
       <c r="I936" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>6.58</v>
       </c>
       <c r="H937" t="n">
-        <v>0.09955016488909063</v>
+        <v>0.09791872142961666</v>
       </c>
       <c r="I937" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>10.97</v>
       </c>
       <c r="H938" t="n">
-        <v>0.2091037183693084</v>
+        <v>0.2046923786931713</v>
       </c>
       <c r="I938" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>19.07</v>
       </c>
       <c r="H939" t="n">
-        <v>0.1397686271317302</v>
+        <v>0.1412617009096189</v>
       </c>
       <c r="I939" t="inlineStr">
         <is>
@@ -29576,7 +29576,7 @@
         <v>5.29</v>
       </c>
       <c r="H940" t="n">
-        <v>0.1145263739831557</v>
+        <v>0.1176135405427126</v>
       </c>
       <c r="I940" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>12.95</v>
       </c>
       <c r="H941" t="n">
-        <v>0.2244832878313732</v>
+        <v>0.2145197045870186</v>
       </c>
       <c r="I941" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>7.72</v>
       </c>
       <c r="H942" t="n">
-        <v>0.2170940794171176</v>
+        <v>0.2116459181694598</v>
       </c>
       <c r="I942" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>28.27</v>
       </c>
       <c r="H943" t="n">
-        <v>0.1303234167727079</v>
+        <v>0.1269770249878652</v>
       </c>
       <c r="I943" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>1.8</v>
       </c>
       <c r="H944" t="n">
-        <v>0.1253763985077666</v>
+        <v>0.1237729941629483</v>
       </c>
       <c r="I944" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>67.77</v>
       </c>
       <c r="H945" t="n">
-        <v>0.1703958803922178</v>
+        <v>0.1665480160139363</v>
       </c>
       <c r="I945" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>5.82</v>
       </c>
       <c r="H946" t="n">
-        <v>0.02353463136042866</v>
+        <v>0.008868249243610848</v>
       </c>
       <c r="I946" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>7.69</v>
       </c>
       <c r="H947" t="n">
-        <v>0.03287526272466978</v>
+        <v>0.02894179025140786</v>
       </c>
       <c r="I947" t="inlineStr">
         <is>
@@ -29824,7 +29824,7 @@
         <v>36.18</v>
       </c>
       <c r="H948" t="n">
-        <v>0.2148146847770113</v>
+        <v>0.210897963699872</v>
       </c>
       <c r="I948" t="inlineStr">
         <is>
@@ -29855,7 +29855,7 @@
         <v>60.71</v>
       </c>
       <c r="H949" t="n">
-        <v>0.1882654353625421</v>
+        <v>0.1782052855929182</v>
       </c>
       <c r="I949" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>156.37</v>
       </c>
       <c r="H950" t="n">
-        <v>0.05125960693162834</v>
+        <v>0.0418783814152921</v>
       </c>
       <c r="I950" t="inlineStr">
         <is>
@@ -29917,7 +29917,7 @@
         <v>35.23</v>
       </c>
       <c r="H951" t="n">
-        <v>0.09766229331699749</v>
+        <v>0.09868693214187785</v>
       </c>
       <c r="I951" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>17.71</v>
       </c>
       <c r="H952" t="n">
-        <v>0.1241207607128427</v>
+        <v>0.121440357112868</v>
       </c>
       <c r="I952" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H953" t="n">
-        <v>0.1432163669101063</v>
+        <v>0.1344622433647198</v>
       </c>
       <c r="I953" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>67.94</v>
       </c>
       <c r="H954" t="n">
-        <v>0.07560516902321446</v>
+        <v>0.07757554308957537</v>
       </c>
       <c r="I954" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>1.01</v>
       </c>
       <c r="H955" t="n">
-        <v>0.1166299769320364</v>
+        <v>0.1140973848286539</v>
       </c>
       <c r="I955" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>3.08</v>
       </c>
       <c r="H956" t="n">
-        <v>0.0773371814403655</v>
+        <v>0.06816617430596184</v>
       </c>
       <c r="I956" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>10.31</v>
       </c>
       <c r="H957" t="n">
-        <v>0.0426477659417559</v>
+        <v>0.04593835468975271</v>
       </c>
       <c r="I957" t="inlineStr">
         <is>
@@ -30134,7 +30134,7 @@
         <v>60.22</v>
       </c>
       <c r="H958" t="n">
-        <v>0.06620381321602897</v>
+        <v>0.06123217067942921</v>
       </c>
       <c r="I958" t="inlineStr">
         <is>
@@ -30165,7 +30165,7 @@
         <v>21.57</v>
       </c>
       <c r="H959" t="n">
-        <v>0.1176845428860523</v>
+        <v>0.1138634893669677</v>
       </c>
       <c r="I959" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>35.35</v>
       </c>
       <c r="H960" t="n">
-        <v>0.2277535697171607</v>
+        <v>0.2217336982508584</v>
       </c>
       <c r="I960" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>111.2</v>
       </c>
       <c r="H961" t="n">
-        <v>0.02327908796959444</v>
+        <v>0.01573897638156063</v>
       </c>
       <c r="I961" t="inlineStr">
         <is>
@@ -30258,7 +30258,7 @@
         <v>136.19</v>
       </c>
       <c r="H962" t="n">
-        <v>0.06961034696739399</v>
+        <v>0.06683448017775884</v>
       </c>
       <c r="I962" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>13.87</v>
       </c>
       <c r="H963" t="n">
-        <v>0.1447760061807788</v>
+        <v>0.1406650656603279</v>
       </c>
       <c r="I963" t="inlineStr">
         <is>
@@ -30320,7 +30320,7 @@
         <v>22.15</v>
       </c>
       <c r="H964" t="n">
-        <v>0.02951292203638667</v>
+        <v>0.01916843666266899</v>
       </c>
       <c r="I964" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>28.93</v>
       </c>
       <c r="H965" t="n">
-        <v>0.07178071226230387</v>
+        <v>0.07680902052704974</v>
       </c>
       <c r="I965" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>58.95</v>
       </c>
       <c r="H966" t="n">
-        <v>0.03993899312281091</v>
+        <v>0.03780461658938883</v>
       </c>
       <c r="I966" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>15.32</v>
       </c>
       <c r="H967" t="n">
-        <v>0.2285643320867078</v>
+        <v>0.2221454888527744</v>
       </c>
       <c r="I967" t="inlineStr">
         <is>
@@ -30444,7 +30444,7 @@
         <v>162.76</v>
       </c>
       <c r="H968" t="n">
-        <v>-0.05209127449805895</v>
+        <v>-0.05945286301379094</v>
       </c>
       <c r="I968" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>17.53</v>
       </c>
       <c r="H969" t="n">
-        <v>0.2284208656531838</v>
+        <v>0.2229444172759152</v>
       </c>
       <c r="I969" t="inlineStr">
         <is>
@@ -30506,7 +30506,7 @@
         <v>26.15</v>
       </c>
       <c r="H970" t="n">
-        <v>-0.01486791075479321</v>
+        <v>-0.02099430654131507</v>
       </c>
       <c r="I970" t="inlineStr">
         <is>
@@ -30537,7 +30537,7 @@
         <v>10.39</v>
       </c>
       <c r="H971" t="n">
-        <v>0.2087589748595253</v>
+        <v>0.2026973497150886</v>
       </c>
       <c r="I971" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>16.34</v>
       </c>
       <c r="H972" t="n">
-        <v>0.1421442819797403</v>
+        <v>0.1325034165275691</v>
       </c>
       <c r="I972" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>6.37</v>
       </c>
       <c r="H973" t="n">
-        <v>0.1317699032254361</v>
+        <v>0.1276306540090028</v>
       </c>
       <c r="I973" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>8.359999999999999</v>
       </c>
       <c r="H974" t="n">
-        <v>0.1310734557258459</v>
+        <v>0.1280667555058226</v>
       </c>
       <c r="I974" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>27.46</v>
       </c>
       <c r="H975" t="n">
-        <v>0.213323752713429</v>
+        <v>0.2121666740068128</v>
       </c>
       <c r="I975" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>9.42</v>
       </c>
       <c r="H976" t="n">
-        <v>0.2190419852787604</v>
+        <v>0.2156867328230328</v>
       </c>
       <c r="I976" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>20.25</v>
       </c>
       <c r="H977" t="n">
-        <v>0.06353361078522124</v>
+        <v>0.060901725346446</v>
       </c>
       <c r="I977" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>10.01</v>
       </c>
       <c r="H978" t="n">
-        <v>0.1439788968999763</v>
+        <v>0.1484018726386739</v>
       </c>
       <c r="I978" t="inlineStr">
         <is>
@@ -30785,7 +30785,7 @@
         <v>26.84</v>
       </c>
       <c r="H979" t="n">
-        <v>0.2364530313150935</v>
+        <v>0.2259836396575192</v>
       </c>
       <c r="I979" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>0.57</v>
       </c>
       <c r="H980" t="n">
-        <v>0.1062215152127554</v>
+        <v>0.1022130222798415</v>
       </c>
       <c r="I980" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>5.24</v>
       </c>
       <c r="H981" t="n">
-        <v>0.127961928438636</v>
+        <v>0.1270348666745491</v>
       </c>
       <c r="I981" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>34.02</v>
       </c>
       <c r="H982" t="n">
-        <v>-0.01180624503065797</v>
+        <v>-0.02234249376338759</v>
       </c>
       <c r="I982" t="inlineStr">
         <is>
@@ -30909,7 +30909,7 @@
         <v>7.15</v>
       </c>
       <c r="H983" t="n">
-        <v>0.05135347130391577</v>
+        <v>0.06089344440905542</v>
       </c>
       <c r="I983" t="inlineStr">
         <is>
@@ -30940,7 +30940,7 @@
         <v>9.91</v>
       </c>
       <c r="H984" t="n">
-        <v>0.2277005186171532</v>
+        <v>0.2232109784957669</v>
       </c>
       <c r="I984" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>5</v>
       </c>
       <c r="H985" t="n">
-        <v>0.2163340310171514</v>
+        <v>0.2121473103529956</v>
       </c>
       <c r="I985" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>39.97</v>
       </c>
       <c r="H986" t="n">
-        <v>0.107127879758829</v>
+        <v>0.1007566300289119</v>
       </c>
       <c r="I986" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>32.01</v>
       </c>
       <c r="H987" t="n">
-        <v>0.06726823211103694</v>
+        <v>0.07472848597140846</v>
       </c>
       <c r="I987" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>6.62</v>
       </c>
       <c r="H988" t="n">
-        <v>0.1178911681182035</v>
+        <v>0.1206128226291725</v>
       </c>
       <c r="I988" t="inlineStr">
         <is>
@@ -31095,7 +31095,7 @@
         <v>72.06999999999999</v>
       </c>
       <c r="H989" t="n">
-        <v>0.1335061788646622</v>
+        <v>0.1263488407148773</v>
       </c>
       <c r="I989" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>17.29</v>
       </c>
       <c r="H990" t="n">
-        <v>0.2394463777998267</v>
+        <v>0.2292920467690098</v>
       </c>
       <c r="I990" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>1.99</v>
       </c>
       <c r="H991" t="n">
-        <v>0.05629016013109778</v>
+        <v>0.05628870816978637</v>
       </c>
       <c r="I991" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>4.28</v>
       </c>
       <c r="H992" t="n">
-        <v>-0.0119323050441783</v>
+        <v>-0.01343739605142558</v>
       </c>
       <c r="I992" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>43.79</v>
       </c>
       <c r="H993" t="n">
-        <v>0.06799692775331734</v>
+        <v>0.06432681373138371</v>
       </c>
       <c r="I993" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>24.38</v>
       </c>
       <c r="H994" t="n">
-        <v>0.2389737274096765</v>
+        <v>0.2289138917311257</v>
       </c>
       <c r="I994" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>53.01</v>
       </c>
       <c r="H995" t="n">
-        <v>0.2065717416339994</v>
+        <v>0.1850622083960099</v>
       </c>
       <c r="I995" t="inlineStr">
         <is>
@@ -31312,7 +31312,7 @@
         <v>5.82</v>
       </c>
       <c r="H996" t="n">
-        <v>0.199534487473837</v>
+        <v>0.1880397985177409</v>
       </c>
       <c r="I996" t="inlineStr">
         <is>
@@ -31343,7 +31343,7 @@
         <v>6.16</v>
       </c>
       <c r="H997" t="n">
-        <v>0.1269788757100576</v>
+        <v>0.1262456361434725</v>
       </c>
       <c r="I997" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>8.140000000000001</v>
       </c>
       <c r="H998" t="n">
-        <v>0.1145030457923958</v>
+        <v>0.1142870591665277</v>
       </c>
       <c r="I998" t="inlineStr">
         <is>
@@ -31405,7 +31405,7 @@
         <v>26.4</v>
       </c>
       <c r="H999" t="n">
-        <v>0.1838486280126167</v>
+        <v>0.1862815671754477</v>
       </c>
       <c r="I999" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>21.09</v>
       </c>
       <c r="H1000" t="n">
-        <v>0.2265085273092215</v>
+        <v>0.2195769512431107</v>
       </c>
       <c r="I1000" t="inlineStr">
         <is>
@@ -31467,9 +31467,443 @@
         <v>28.12</v>
       </c>
       <c r="H1001" t="n">
-        <v>0.09047043888476702</v>
+        <v>0.09844994002247565</v>
       </c>
       <c r="I1001" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>5.014</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>0.1170913670602084</v>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>1.153</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>0.1539908085163048</v>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>1.879</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>0.1577505652148775</v>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1005" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>0.1536149097451857</v>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1006" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>0.1510276682400852</v>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1007" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>0.152969661472678</v>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1008" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1008" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>0.1206669110525089</v>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1009" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>0.1524141050489974</v>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1010" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>1.161</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>0.1549303207567019</v>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1011" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>0.1180923368082751</v>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1012" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>0.1526455342654355</v>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1013" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>0.153084129756966</v>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1014" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>0.1524141050489974</v>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="n">
+        <v>1</v>
+      </c>
+      <c r="B1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>1</v>
+      </c>
+      <c r="F1015" t="n">
+        <v>2</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>0.1524141050489974</v>
+      </c>
+      <c r="I1015" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
